--- a/api/clv3/xlsx/fr/OrganisationRegistrationAgency.xlsx
+++ b/api/clv3/xlsx/fr/OrganisationRegistrationAgency.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>iso-alpha-3-code</t>
   </si>
   <si>
     <t>region-code</t>
   </si>
   <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
+    <t>global-name</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
     <t>sub-region-name</t>
   </si>
   <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>global-name</t>
-  </si>
-  <si>
     <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
-    <t>global-code</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
   </si>
   <si>
     <t>AE-ACCI</t>

--- a/api/clv3/xlsx/fr/OrganisationRegistrationAgency.xlsx
+++ b/api/clv3/xlsx/fr/OrganisationRegistrationAgency.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>intermediate-region-name</t>
   </si>
   <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
     <t>sub-region-code</t>
   </si>
   <si>
-    <t>global-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
-  </si>
-  <si>
     <t>global-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
   </si>
   <si>
     <t>AE-ACCI</t>

--- a/api/clv3/xlsx/fr/OrganisationRegistrationAgency.xlsx
+++ b/api/clv3/xlsx/fr/OrganisationRegistrationAgency.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>global-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
     <t>global-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
-  </si>
-  <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>global-name</t>
   </si>
   <si>
     <t>AE-ACCI</t>

--- a/api/clv3/xlsx/fr/OrganisationRegistrationAgency.xlsx
+++ b/api/clv3/xlsx/fr/OrganisationRegistrationAgency.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>global-name</t>
   </si>
   <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
     <t>region-code</t>
   </si>
   <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
     <t>region-name</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
-  </si>
-  <si>
-    <t>global-code</t>
   </si>
   <si>
     <t>AE-ACCI</t>

--- a/api/clv3/xlsx/fr/OrganisationRegistrationAgency.xlsx
+++ b/api/clv3/xlsx/fr/OrganisationRegistrationAgency.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>global-name</t>
+  </si>
+  <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
     <t>intermediate-region-name</t>
   </si>
   <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
     <t>intermediate-region-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>global-code</t>
-  </si>
-  <si>
-    <t>global-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
   </si>
   <si>
     <t>AE-ACCI</t>

--- a/api/clv3/xlsx/fr/OrganisationRegistrationAgency.xlsx
+++ b/api/clv3/xlsx/fr/OrganisationRegistrationAgency.xlsx
@@ -40,34 +40,34 @@
     <t>budget_alignment_guidance</t>
   </si>
   <si>
+    <t>iso-alpha-3-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-code</t>
+  </si>
+  <si>
+    <t>intermediate-region-name</t>
+  </si>
+  <si>
     <t>global-name</t>
   </si>
   <si>
+    <t>region-name</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
     <t>sub-region-code</t>
   </si>
   <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
     <t>global-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-3-code</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>intermediate-region-name</t>
-  </si>
-  <si>
-    <t>intermediate-region-code</t>
   </si>
   <si>
     <t>AE-ACCI</t>

--- a/api/clv3/xlsx/fr/OrganisationRegistrationAgency.xlsx
+++ b/api/clv3/xlsx/fr/OrganisationRegistrationAgency.xlsx
@@ -43,31 +43,31 @@
     <t>iso-alpha-3-code</t>
   </si>
   <si>
+    <t>sub-region-name</t>
+  </si>
+  <si>
     <t>intermediate-region-code</t>
   </si>
   <si>
+    <t>sub-region-code</t>
+  </si>
+  <si>
+    <t>region-code</t>
+  </si>
+  <si>
+    <t>global-code</t>
+  </si>
+  <si>
     <t>intermediate-region-name</t>
   </si>
   <si>
+    <t>iso-alpha-2-code</t>
+  </si>
+  <si>
+    <t>region-name</t>
+  </si>
+  <si>
     <t>global-name</t>
-  </si>
-  <si>
-    <t>region-name</t>
-  </si>
-  <si>
-    <t>region-code</t>
-  </si>
-  <si>
-    <t>sub-region-code</t>
-  </si>
-  <si>
-    <t>sub-region-name</t>
-  </si>
-  <si>
-    <t>iso-alpha-2-code</t>
-  </si>
-  <si>
-    <t>global-code</t>
   </si>
   <si>
     <t>AE-ACCI</t>

--- a/api/clv3/xlsx/fr/OrganisationRegistrationAgency.xlsx
+++ b/api/clv3/xlsx/fr/OrganisationRegistrationAgency.xlsx
@@ -14,15 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="479">
   <si>
     <t>code</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>description</t>
   </si>
   <si>
     <t>category</t>
@@ -1801,10 +1795,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G198"/>
+  <dimension ref="A1:E198"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1820,3541 +1814,3535 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
         <v>17</v>
       </c>
-      <c r="D6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="D7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="D8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
         <v>23</v>
       </c>
-      <c r="D9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
         <v>25</v>
       </c>
-      <c r="D10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
         <v>27</v>
       </c>
-      <c r="D11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
         <v>29</v>
       </c>
-      <c r="D12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
+      <c r="D13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
         <v>31</v>
       </c>
-      <c r="D13" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
         <v>33</v>
       </c>
-      <c r="D14" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
+      <c r="D15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
         <v>35</v>
       </c>
-      <c r="D15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="1" t="s">
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
+      <c r="D16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
         <v>37</v>
       </c>
-      <c r="D16" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="B17" t="s">
         <v>38</v>
       </c>
-      <c r="F16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
+      <c r="C17" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F17" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
+      <c r="D18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
         <v>42</v>
       </c>
-      <c r="D18" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="B19" t="s">
         <v>43</v>
       </c>
-      <c r="F18" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
+      <c r="C19" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="B20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
         <v>46</v>
       </c>
-      <c r="F19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" t="s">
+      <c r="B21" t="s">
         <v>47</v>
       </c>
-      <c r="D20" t="s">
-        <v>45</v>
-      </c>
-      <c r="F20" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" t="s">
+      <c r="C21" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
         <v>49</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="B22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
         <v>50</v>
       </c>
-      <c r="F21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" t="s">
+      <c r="B23" t="s">
         <v>51</v>
       </c>
-      <c r="D22" t="s">
-        <v>49</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" t="s">
+      <c r="C23" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
         <v>53</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="B24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F23" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" t="s">
+      <c r="D24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
         <v>55</v>
       </c>
-      <c r="D24" t="s">
-        <v>53</v>
-      </c>
-      <c r="E24" s="1" t="s">
+      <c r="B25" t="s">
         <v>56</v>
       </c>
-      <c r="F24" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" t="s">
+      <c r="C25" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
         <v>58</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="B26" t="s">
         <v>59</v>
       </c>
-      <c r="F25" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" t="s">
+      <c r="C26" s="1" t="s">
         <v>60</v>
       </c>
       <c r="D26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
         <v>61</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="B27" t="s">
         <v>62</v>
       </c>
-      <c r="F26" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" t="s">
+      <c r="C27" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D27" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
         <v>64</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="B28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F27" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" t="s">
+      <c r="D28" t="s">
         <v>66</v>
       </c>
-      <c r="D28" t="s">
-        <v>64</v>
-      </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
         <v>67</v>
       </c>
-      <c r="F28" t="s">
+      <c r="B29" t="s">
         <v>68</v>
       </c>
-      <c r="G28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" t="s">
+      <c r="C29" s="1" t="s">
         <v>69</v>
       </c>
       <c r="D29" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
         <v>70</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="B30" t="s">
         <v>71</v>
       </c>
-      <c r="F29" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" t="s">
+      <c r="C30" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D30" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
         <v>73</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="B31" t="s">
         <v>74</v>
       </c>
-      <c r="F30" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" t="s">
+      <c r="C31" s="1" t="s">
         <v>75</v>
       </c>
       <c r="D31" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
         <v>76</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="B32" t="s">
         <v>77</v>
       </c>
-      <c r="F31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" t="s">
+      <c r="C32" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D32" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
         <v>79</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="B33" t="s">
         <v>80</v>
       </c>
-      <c r="F32" t="s">
-        <v>10</v>
-      </c>
-      <c r="G32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" t="s">
+      <c r="C33" s="1" t="s">
         <v>81</v>
       </c>
       <c r="D33" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
         <v>82</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="B34" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" t="s">
+      <c r="D34" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
         <v>84</v>
       </c>
-      <c r="D34" t="s">
-        <v>82</v>
-      </c>
-      <c r="E34" s="1" t="s">
+      <c r="B35" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F34" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" t="s">
+      <c r="D35" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
         <v>86</v>
       </c>
-      <c r="D35" t="s">
-        <v>82</v>
-      </c>
-      <c r="E35" s="1" t="s">
+      <c r="B36" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F35" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" t="s">
+      <c r="D36" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
         <v>88</v>
       </c>
-      <c r="D36" t="s">
-        <v>82</v>
-      </c>
-      <c r="E36" s="1" t="s">
+      <c r="B37" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F36" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" t="s">
+      <c r="D37" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
         <v>90</v>
       </c>
-      <c r="D37" t="s">
-        <v>82</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="B38" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F37" t="s">
-        <v>10</v>
-      </c>
-      <c r="G37" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" t="s">
+      <c r="D38" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
         <v>92</v>
       </c>
-      <c r="D38" t="s">
-        <v>82</v>
-      </c>
-      <c r="E38" s="1" t="s">
+      <c r="B39" t="s">
+        <v>80</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F38" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" t="s">
+      <c r="D39" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
         <v>94</v>
       </c>
-      <c r="D39" t="s">
-        <v>82</v>
-      </c>
-      <c r="E39" s="1" t="s">
+      <c r="B40" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F39" t="s">
-        <v>10</v>
-      </c>
-      <c r="G39" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" t="s">
+      <c r="D40" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
         <v>96</v>
       </c>
-      <c r="D40" t="s">
-        <v>82</v>
-      </c>
-      <c r="E40" s="1" t="s">
+      <c r="B41" t="s">
+        <v>80</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F40" t="s">
-        <v>10</v>
-      </c>
-      <c r="G40" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" t="s">
+      <c r="D41" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
         <v>98</v>
       </c>
-      <c r="D41" t="s">
-        <v>82</v>
-      </c>
-      <c r="E41" s="1" t="s">
+      <c r="B42" t="s">
+        <v>80</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F41" t="s">
-        <v>10</v>
-      </c>
-      <c r="G41" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42" t="s">
+      <c r="D42" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
         <v>100</v>
       </c>
-      <c r="D42" t="s">
-        <v>82</v>
-      </c>
-      <c r="E42" s="1" t="s">
+      <c r="B43" t="s">
+        <v>80</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F42" t="s">
-        <v>10</v>
-      </c>
-      <c r="G42" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" t="s">
+      <c r="D43" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
         <v>102</v>
       </c>
-      <c r="D43" t="s">
-        <v>82</v>
-      </c>
-      <c r="E43" s="1" t="s">
+      <c r="B44" t="s">
+        <v>80</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F43" t="s">
-        <v>10</v>
-      </c>
-      <c r="G43" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" t="s">
+      <c r="D44" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
         <v>104</v>
       </c>
-      <c r="D44" t="s">
-        <v>82</v>
-      </c>
-      <c r="E44" s="1" t="s">
+      <c r="B45" t="s">
+        <v>80</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F44" t="s">
-        <v>10</v>
-      </c>
-      <c r="G44" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" t="s">
+      <c r="D45" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
         <v>106</v>
       </c>
-      <c r="D45" t="s">
-        <v>82</v>
-      </c>
-      <c r="E45" s="1" t="s">
+      <c r="B46" t="s">
+        <v>80</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="F45" t="s">
-        <v>10</v>
-      </c>
-      <c r="G45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" t="s">
+      <c r="D46" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
         <v>108</v>
       </c>
-      <c r="D46" t="s">
-        <v>82</v>
-      </c>
-      <c r="E46" s="1" t="s">
+      <c r="B47" t="s">
+        <v>80</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F46" t="s">
-        <v>10</v>
-      </c>
-      <c r="G46" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" t="s">
+      <c r="D47" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
         <v>110</v>
       </c>
-      <c r="D47" t="s">
-        <v>82</v>
-      </c>
-      <c r="E47" s="1" t="s">
+      <c r="B48" t="s">
+        <v>80</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="F47" t="s">
-        <v>10</v>
-      </c>
-      <c r="G47" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" t="s">
+      <c r="D48" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
         <v>112</v>
       </c>
-      <c r="D48" t="s">
-        <v>82</v>
-      </c>
-      <c r="E48" s="1" t="s">
+      <c r="B49" t="s">
         <v>113</v>
       </c>
-      <c r="F48" t="s">
-        <v>10</v>
-      </c>
-      <c r="G48" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" t="s">
+      <c r="C49" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D49" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
         <v>115</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="B50" t="s">
         <v>116</v>
       </c>
-      <c r="F49" t="s">
-        <v>10</v>
-      </c>
-      <c r="G49" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" t="s">
+      <c r="C50" s="1" t="s">
         <v>117</v>
       </c>
       <c r="D50" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
         <v>118</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="B51" t="s">
         <v>119</v>
       </c>
-      <c r="F50" t="s">
-        <v>10</v>
-      </c>
-      <c r="G50" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" t="s">
+      <c r="C51" s="1" t="s">
         <v>120</v>
       </c>
       <c r="D51" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
         <v>121</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="B52" t="s">
+        <v>119</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F51" t="s">
-        <v>10</v>
-      </c>
-      <c r="G51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" t="s">
+      <c r="D52" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
         <v>123</v>
       </c>
-      <c r="D52" t="s">
-        <v>121</v>
-      </c>
-      <c r="E52" s="1" t="s">
+      <c r="B53" t="s">
         <v>124</v>
       </c>
-      <c r="F52" t="s">
-        <v>10</v>
-      </c>
-      <c r="G52" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" t="s">
+      <c r="C53" s="1" t="s">
         <v>125</v>
       </c>
       <c r="D53" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
         <v>126</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="B54" t="s">
         <v>127</v>
       </c>
-      <c r="F53" t="s">
-        <v>10</v>
-      </c>
-      <c r="G53" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" t="s">
+      <c r="C54" s="1" t="s">
         <v>128</v>
       </c>
       <c r="D54" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
         <v>129</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="B55" t="s">
+        <v>127</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F54" t="s">
-        <v>10</v>
-      </c>
-      <c r="G54" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" t="s">
+      <c r="D55" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
         <v>131</v>
       </c>
-      <c r="D55" t="s">
-        <v>129</v>
-      </c>
-      <c r="E55" s="1" t="s">
+      <c r="B56" t="s">
         <v>132</v>
       </c>
-      <c r="F55" t="s">
-        <v>10</v>
-      </c>
-      <c r="G55" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56" t="s">
+      <c r="C56" s="1" t="s">
         <v>133</v>
       </c>
       <c r="D56" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
         <v>134</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="B57" t="s">
         <v>135</v>
       </c>
-      <c r="F56" t="s">
-        <v>10</v>
-      </c>
-      <c r="G56" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57" t="s">
+      <c r="C57" s="1" t="s">
         <v>136</v>
       </c>
       <c r="D57" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
         <v>137</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="B58" t="s">
         <v>138</v>
       </c>
-      <c r="F57" t="s">
-        <v>10</v>
-      </c>
-      <c r="G57" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" t="s">
+      <c r="C58" s="1" t="s">
         <v>139</v>
       </c>
       <c r="D58" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
         <v>140</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="B59" t="s">
+        <v>138</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D59" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
         <v>141</v>
       </c>
-      <c r="F58" t="s">
-        <v>10</v>
-      </c>
-      <c r="G58" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59" t="s">
+      <c r="B60" t="s">
         <v>142</v>
       </c>
-      <c r="D59" t="s">
-        <v>140</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F59" t="s">
-        <v>10</v>
-      </c>
-      <c r="G59" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60" t="s">
+      <c r="C60" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D60" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
         <v>144</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="B61" t="s">
         <v>145</v>
       </c>
-      <c r="F60" t="s">
-        <v>10</v>
-      </c>
-      <c r="G60" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61" t="s">
+      <c r="C61" s="1" t="s">
         <v>146</v>
       </c>
       <c r="D61" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
         <v>147</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="B62" t="s">
+        <v>145</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F61" t="s">
-        <v>10</v>
-      </c>
-      <c r="G61" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62" t="s">
+      <c r="D62" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
         <v>149</v>
       </c>
-      <c r="D62" t="s">
-        <v>147</v>
-      </c>
-      <c r="E62" s="1" t="s">
+      <c r="B63" t="s">
         <v>150</v>
       </c>
-      <c r="F62" t="s">
-        <v>10</v>
-      </c>
-      <c r="G62" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63" t="s">
+      <c r="C63" s="1" t="s">
         <v>151</v>
       </c>
       <c r="D63" t="s">
+        <v>8</v>
+      </c>
+      <c r="E63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
         <v>152</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="B64" t="s">
+        <v>150</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="F63" t="s">
-        <v>10</v>
-      </c>
-      <c r="G63" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64" t="s">
+      <c r="D64" t="s">
+        <v>8</v>
+      </c>
+      <c r="E64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
         <v>154</v>
       </c>
-      <c r="D64" t="s">
-        <v>152</v>
-      </c>
-      <c r="E64" s="1" t="s">
+      <c r="B65" t="s">
+        <v>150</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F64" t="s">
-        <v>10</v>
-      </c>
-      <c r="G64" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65" t="s">
+      <c r="D65" t="s">
+        <v>8</v>
+      </c>
+      <c r="E65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
         <v>156</v>
       </c>
-      <c r="D65" t="s">
-        <v>152</v>
-      </c>
-      <c r="E65" s="1" t="s">
+      <c r="B66" t="s">
         <v>157</v>
       </c>
-      <c r="F65" t="s">
-        <v>10</v>
-      </c>
-      <c r="G65" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66" t="s">
+      <c r="C66" s="1" t="s">
         <v>158</v>
       </c>
       <c r="D66" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
         <v>159</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="B67" t="s">
         <v>160</v>
       </c>
-      <c r="F66" t="s">
-        <v>10</v>
-      </c>
-      <c r="G66" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67" t="s">
+      <c r="C67" s="1" t="s">
         <v>161</v>
       </c>
       <c r="D67" t="s">
+        <v>66</v>
+      </c>
+      <c r="E67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
         <v>162</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="B68" t="s">
+        <v>160</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="F67" t="s">
-        <v>68</v>
-      </c>
-      <c r="G67" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68" t="s">
+      <c r="D68" t="s">
+        <v>8</v>
+      </c>
+      <c r="E68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
         <v>164</v>
       </c>
-      <c r="D68" t="s">
-        <v>162</v>
-      </c>
-      <c r="E68" s="1" t="s">
+      <c r="B69" t="s">
         <v>165</v>
       </c>
-      <c r="F68" t="s">
-        <v>10</v>
-      </c>
-      <c r="G68" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69" t="s">
+      <c r="C69" s="1" t="s">
         <v>166</v>
       </c>
       <c r="D69" t="s">
+        <v>8</v>
+      </c>
+      <c r="E69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
         <v>167</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="B70" t="s">
+        <v>165</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="F69" t="s">
-        <v>10</v>
-      </c>
-      <c r="G69" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" t="s">
+      <c r="D70" t="s">
+        <v>8</v>
+      </c>
+      <c r="E70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
         <v>169</v>
       </c>
-      <c r="D70" t="s">
-        <v>167</v>
-      </c>
-      <c r="E70" s="1" t="s">
+      <c r="B71" t="s">
+        <v>165</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F70" t="s">
-        <v>10</v>
-      </c>
-      <c r="G70" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
-      <c r="A71" t="s">
+      <c r="D71" t="s">
+        <v>8</v>
+      </c>
+      <c r="E71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
         <v>171</v>
       </c>
-      <c r="D71" t="s">
-        <v>167</v>
-      </c>
-      <c r="E71" s="1" t="s">
+      <c r="B72" t="s">
+        <v>165</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="F71" t="s">
-        <v>10</v>
-      </c>
-      <c r="G71" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
-      <c r="A72" t="s">
+      <c r="D72" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
         <v>173</v>
       </c>
-      <c r="D72" t="s">
-        <v>167</v>
-      </c>
-      <c r="E72" s="1" t="s">
+      <c r="B73" t="s">
+        <v>165</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F72" t="s">
-        <v>10</v>
-      </c>
-      <c r="G72" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
-      <c r="A73" t="s">
+      <c r="D73" t="s">
+        <v>8</v>
+      </c>
+      <c r="E73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
         <v>175</v>
       </c>
-      <c r="D73" t="s">
-        <v>167</v>
-      </c>
-      <c r="E73" s="1" t="s">
+      <c r="B74" t="s">
+        <v>165</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="F73" t="s">
-        <v>10</v>
-      </c>
-      <c r="G73" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
-      <c r="A74" t="s">
+      <c r="D74" t="s">
+        <v>66</v>
+      </c>
+      <c r="E74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
         <v>177</v>
       </c>
-      <c r="D74" t="s">
-        <v>167</v>
-      </c>
-      <c r="E74" s="1" t="s">
+      <c r="B75" t="s">
+        <v>165</v>
+      </c>
+      <c r="C75" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="F74" t="s">
-        <v>68</v>
-      </c>
-      <c r="G74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
-      <c r="A75" t="s">
+      <c r="D75" t="s">
+        <v>8</v>
+      </c>
+      <c r="E75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
         <v>179</v>
       </c>
-      <c r="D75" t="s">
-        <v>167</v>
-      </c>
-      <c r="E75" s="1" t="s">
+      <c r="B76" t="s">
+        <v>165</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F75" t="s">
-        <v>10</v>
-      </c>
-      <c r="G75" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
-      <c r="A76" t="s">
+      <c r="D76" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
         <v>181</v>
       </c>
-      <c r="D76" t="s">
-        <v>167</v>
-      </c>
-      <c r="E76" s="1" t="s">
+      <c r="B77" t="s">
+        <v>165</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F76" t="s">
-        <v>10</v>
-      </c>
-      <c r="G76" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
-      <c r="A77" t="s">
+      <c r="D77" t="s">
+        <v>8</v>
+      </c>
+      <c r="E77" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
         <v>183</v>
       </c>
-      <c r="D77" t="s">
-        <v>167</v>
-      </c>
-      <c r="E77" s="1" t="s">
+      <c r="B78" t="s">
+        <v>165</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F77" t="s">
-        <v>10</v>
-      </c>
-      <c r="G77" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78" t="s">
+      <c r="D78" t="s">
+        <v>8</v>
+      </c>
+      <c r="E78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
         <v>185</v>
       </c>
-      <c r="D78" t="s">
-        <v>167</v>
-      </c>
-      <c r="E78" s="1" t="s">
+      <c r="B79" t="s">
+        <v>165</v>
+      </c>
+      <c r="C79" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="F78" t="s">
-        <v>10</v>
-      </c>
-      <c r="G78" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
-      <c r="A79" t="s">
+      <c r="D79" t="s">
+        <v>8</v>
+      </c>
+      <c r="E79" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
         <v>187</v>
       </c>
-      <c r="D79" t="s">
-        <v>167</v>
-      </c>
-      <c r="E79" s="1" t="s">
+      <c r="B80" t="s">
+        <v>165</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F79" t="s">
-        <v>10</v>
-      </c>
-      <c r="G79" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
-      <c r="A80" t="s">
+      <c r="D80" t="s">
+        <v>8</v>
+      </c>
+      <c r="E80" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
         <v>189</v>
       </c>
-      <c r="D80" t="s">
-        <v>167</v>
-      </c>
-      <c r="E80" s="1" t="s">
+      <c r="B81" t="s">
+        <v>165</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F80" t="s">
-        <v>10</v>
-      </c>
-      <c r="G80" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
-      <c r="A81" t="s">
+      <c r="D81" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
         <v>191</v>
       </c>
-      <c r="D81" t="s">
-        <v>167</v>
-      </c>
-      <c r="E81" s="1" t="s">
+      <c r="B82" t="s">
+        <v>165</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F81" t="s">
-        <v>10</v>
-      </c>
-      <c r="G81" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
-      <c r="A82" t="s">
+      <c r="D82" t="s">
+        <v>8</v>
+      </c>
+      <c r="E82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
         <v>193</v>
       </c>
-      <c r="D82" t="s">
-        <v>167</v>
-      </c>
-      <c r="E82" s="1" t="s">
+      <c r="B83" t="s">
+        <v>165</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="F82" t="s">
-        <v>10</v>
-      </c>
-      <c r="G82" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
-      <c r="A83" t="s">
+      <c r="D83" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
         <v>195</v>
       </c>
-      <c r="D83" t="s">
-        <v>167</v>
-      </c>
-      <c r="E83" s="1" t="s">
+      <c r="B84" t="s">
+        <v>165</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F83" t="s">
-        <v>10</v>
-      </c>
-      <c r="G83" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7">
-      <c r="A84" t="s">
+      <c r="D84" t="s">
+        <v>8</v>
+      </c>
+      <c r="E84" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
         <v>197</v>
       </c>
-      <c r="D84" t="s">
-        <v>167</v>
-      </c>
-      <c r="E84" s="1" t="s">
+      <c r="B85" t="s">
+        <v>165</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="F84" t="s">
-        <v>10</v>
-      </c>
-      <c r="G84" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7">
-      <c r="A85" t="s">
+      <c r="D85" t="s">
+        <v>8</v>
+      </c>
+      <c r="E85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
         <v>199</v>
       </c>
-      <c r="D85" t="s">
-        <v>167</v>
-      </c>
-      <c r="E85" s="1" t="s">
+      <c r="B86" t="s">
         <v>200</v>
       </c>
-      <c r="F85" t="s">
-        <v>10</v>
-      </c>
-      <c r="G85" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7">
-      <c r="A86" t="s">
+      <c r="C86" s="1" t="s">
         <v>201</v>
       </c>
       <c r="D86" t="s">
+        <v>8</v>
+      </c>
+      <c r="E86" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
         <v>202</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="B87" t="s">
         <v>203</v>
       </c>
-      <c r="F86" t="s">
-        <v>10</v>
-      </c>
-      <c r="G86" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7">
-      <c r="A87" t="s">
+      <c r="C87" s="1" t="s">
         <v>204</v>
       </c>
       <c r="D87" t="s">
+        <v>8</v>
+      </c>
+      <c r="E87" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
         <v>205</v>
       </c>
-      <c r="E87" s="1" t="s">
+      <c r="B88" t="s">
         <v>206</v>
       </c>
-      <c r="F87" t="s">
-        <v>10</v>
-      </c>
-      <c r="G87" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7">
-      <c r="A88" t="s">
+      <c r="C88" s="1" t="s">
         <v>207</v>
       </c>
       <c r="D88" t="s">
+        <v>8</v>
+      </c>
+      <c r="E88" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
         <v>208</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="B89" t="s">
         <v>209</v>
       </c>
-      <c r="F88" t="s">
-        <v>10</v>
-      </c>
-      <c r="G88" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7">
-      <c r="A89" t="s">
+      <c r="C89" s="1" t="s">
         <v>210</v>
       </c>
       <c r="D89" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" t="s">
         <v>211</v>
       </c>
-      <c r="E89" s="1" t="s">
+      <c r="B90" t="s">
         <v>212</v>
       </c>
-      <c r="F89" t="s">
-        <v>10</v>
-      </c>
-      <c r="G89" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7">
-      <c r="A90" t="s">
+      <c r="C90" s="1" t="s">
         <v>213</v>
       </c>
       <c r="D90" t="s">
+        <v>8</v>
+      </c>
+      <c r="E90" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
         <v>214</v>
       </c>
-      <c r="E90" s="1" t="s">
+      <c r="B91" t="s">
+        <v>212</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F90" t="s">
-        <v>10</v>
-      </c>
-      <c r="G90" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7">
-      <c r="A91" t="s">
+      <c r="D91" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
         <v>216</v>
       </c>
-      <c r="D91" t="s">
-        <v>214</v>
-      </c>
-      <c r="E91" s="1" t="s">
+      <c r="B92" t="s">
         <v>217</v>
       </c>
-      <c r="F91" t="s">
-        <v>10</v>
-      </c>
-      <c r="G91" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7">
-      <c r="A92" t="s">
+      <c r="C92" s="1" t="s">
         <v>218</v>
       </c>
       <c r="D92" t="s">
+        <v>8</v>
+      </c>
+      <c r="E92" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" t="s">
         <v>219</v>
       </c>
-      <c r="E92" s="1" t="s">
+      <c r="B93" t="s">
         <v>220</v>
       </c>
-      <c r="F92" t="s">
-        <v>10</v>
-      </c>
-      <c r="G92" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
-      <c r="A93" t="s">
+      <c r="C93" s="1" t="s">
         <v>221</v>
       </c>
       <c r="D93" t="s">
+        <v>66</v>
+      </c>
+      <c r="E93" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" t="s">
         <v>222</v>
       </c>
-      <c r="E93" s="1" t="s">
+      <c r="B94" t="s">
+        <v>220</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F93" t="s">
-        <v>68</v>
-      </c>
-      <c r="G93" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
-      <c r="A94" t="s">
+      <c r="D94" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" t="s">
         <v>224</v>
       </c>
-      <c r="D94" t="s">
-        <v>222</v>
-      </c>
-      <c r="E94" s="1" t="s">
+      <c r="B95" t="s">
+        <v>220</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="F94" t="s">
-        <v>10</v>
-      </c>
-      <c r="G94" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
-      <c r="A95" t="s">
+      <c r="D95" t="s">
+        <v>8</v>
+      </c>
+      <c r="E95" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" t="s">
         <v>226</v>
       </c>
-      <c r="D95" t="s">
-        <v>222</v>
-      </c>
-      <c r="E95" s="1" t="s">
+      <c r="B96" t="s">
+        <v>220</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="F95" t="s">
-        <v>10</v>
-      </c>
-      <c r="G95" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
-      <c r="A96" t="s">
+      <c r="D96" t="s">
+        <v>66</v>
+      </c>
+      <c r="E96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" t="s">
         <v>228</v>
       </c>
-      <c r="D96" t="s">
-        <v>222</v>
-      </c>
-      <c r="E96" s="1" t="s">
+      <c r="B97" t="s">
+        <v>220</v>
+      </c>
+      <c r="C97" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="F96" t="s">
-        <v>68</v>
-      </c>
-      <c r="G96" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
-      <c r="A97" t="s">
+      <c r="D97" t="s">
+        <v>8</v>
+      </c>
+      <c r="E97" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" t="s">
         <v>230</v>
       </c>
-      <c r="D97" t="s">
-        <v>222</v>
-      </c>
-      <c r="E97" s="1" t="s">
+      <c r="B98" t="s">
         <v>231</v>
       </c>
-      <c r="F97" t="s">
-        <v>10</v>
-      </c>
-      <c r="G97" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7">
-      <c r="A98" t="s">
+      <c r="C98" s="1" t="s">
         <v>232</v>
       </c>
       <c r="D98" t="s">
+        <v>8</v>
+      </c>
+      <c r="E98" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" t="s">
         <v>233</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="B99" t="s">
+        <v>231</v>
+      </c>
+      <c r="C99" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="F98" t="s">
-        <v>10</v>
-      </c>
-      <c r="G98" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7">
-      <c r="A99" t="s">
+      <c r="D99" t="s">
+        <v>8</v>
+      </c>
+      <c r="E99" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" t="s">
         <v>235</v>
       </c>
-      <c r="D99" t="s">
-        <v>233</v>
-      </c>
-      <c r="E99" s="1" t="s">
+      <c r="B100" t="s">
         <v>236</v>
       </c>
-      <c r="F99" t="s">
-        <v>10</v>
-      </c>
-      <c r="G99" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
-      <c r="A100" t="s">
+      <c r="C100" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D100" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" t="s">
         <v>238</v>
       </c>
-      <c r="E100" s="1" t="s">
+      <c r="B101" t="s">
         <v>239</v>
       </c>
-      <c r="F100" t="s">
-        <v>10</v>
-      </c>
-      <c r="G100" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7">
-      <c r="A101" t="s">
+      <c r="C101" s="1" t="s">
         <v>240</v>
       </c>
       <c r="D101" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" t="s">
         <v>241</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="B102" t="s">
+        <v>239</v>
+      </c>
+      <c r="C102" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="F101" t="s">
-        <v>10</v>
-      </c>
-      <c r="G101" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7">
-      <c r="A102" t="s">
+      <c r="D102" t="s">
+        <v>8</v>
+      </c>
+      <c r="E102" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" t="s">
         <v>243</v>
       </c>
-      <c r="D102" t="s">
-        <v>241</v>
-      </c>
-      <c r="E102" s="1" t="s">
+      <c r="B103" t="s">
         <v>244</v>
       </c>
-      <c r="F102" t="s">
-        <v>10</v>
-      </c>
-      <c r="G102" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7">
-      <c r="A103" t="s">
+      <c r="C103" s="1" t="s">
         <v>245</v>
       </c>
       <c r="D103" t="s">
+        <v>8</v>
+      </c>
+      <c r="E103" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" t="s">
         <v>246</v>
       </c>
-      <c r="E103" s="1" t="s">
+      <c r="B104" t="s">
+        <v>244</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="F103" t="s">
-        <v>10</v>
-      </c>
-      <c r="G103" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7">
-      <c r="A104" t="s">
+      <c r="D104" t="s">
+        <v>8</v>
+      </c>
+      <c r="E104" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" t="s">
         <v>248</v>
       </c>
-      <c r="D104" t="s">
-        <v>246</v>
-      </c>
-      <c r="E104" s="1" t="s">
+      <c r="B105" t="s">
         <v>249</v>
       </c>
-      <c r="F104" t="s">
-        <v>10</v>
-      </c>
-      <c r="G104" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7">
-      <c r="A105" t="s">
+      <c r="C105" s="1" t="s">
         <v>250</v>
       </c>
       <c r="D105" t="s">
+        <v>8</v>
+      </c>
+      <c r="E105" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" t="s">
         <v>251</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="B106" t="s">
+        <v>249</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D106" t="s">
+        <v>66</v>
+      </c>
+      <c r="E106" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" t="s">
         <v>252</v>
       </c>
-      <c r="F105" t="s">
-        <v>10</v>
-      </c>
-      <c r="G105" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7">
-      <c r="A106" t="s">
+      <c r="B107" t="s">
         <v>253</v>
       </c>
-      <c r="D106" t="s">
-        <v>251</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="F106" t="s">
-        <v>68</v>
-      </c>
-      <c r="G106" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7">
-      <c r="A107" t="s">
+      <c r="C107" s="1" t="s">
         <v>254</v>
       </c>
       <c r="D107" t="s">
+        <v>8</v>
+      </c>
+      <c r="E107" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" t="s">
         <v>255</v>
       </c>
-      <c r="E107" s="1" t="s">
+      <c r="B108" t="s">
+        <v>253</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="F107" t="s">
-        <v>10</v>
-      </c>
-      <c r="G107" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7">
-      <c r="A108" t="s">
+      <c r="D108" t="s">
+        <v>66</v>
+      </c>
+      <c r="E108" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" t="s">
         <v>257</v>
       </c>
-      <c r="D108" t="s">
-        <v>255</v>
-      </c>
-      <c r="E108" s="1" t="s">
+      <c r="B109" t="s">
         <v>258</v>
       </c>
-      <c r="F108" t="s">
-        <v>68</v>
-      </c>
-      <c r="G108" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7">
-      <c r="A109" t="s">
+      <c r="C109" s="1" t="s">
         <v>259</v>
       </c>
       <c r="D109" t="s">
+        <v>8</v>
+      </c>
+      <c r="E109" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" t="s">
         <v>260</v>
       </c>
-      <c r="E109" s="1" t="s">
+      <c r="B110" t="s">
+        <v>258</v>
+      </c>
+      <c r="C110" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="F109" t="s">
-        <v>10</v>
-      </c>
-      <c r="G109" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7">
-      <c r="A110" t="s">
+      <c r="D110" t="s">
+        <v>8</v>
+      </c>
+      <c r="E110" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" t="s">
         <v>262</v>
       </c>
-      <c r="D110" t="s">
-        <v>260</v>
-      </c>
-      <c r="E110" s="1" t="s">
+      <c r="B111" t="s">
         <v>263</v>
       </c>
-      <c r="F110" t="s">
-        <v>10</v>
-      </c>
-      <c r="G110" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7">
-      <c r="A111" t="s">
+      <c r="C111" s="1" t="s">
         <v>264</v>
       </c>
       <c r="D111" t="s">
+        <v>8</v>
+      </c>
+      <c r="E111" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" t="s">
         <v>265</v>
       </c>
-      <c r="E111" s="1" t="s">
+      <c r="B112" t="s">
         <v>266</v>
       </c>
-      <c r="F111" t="s">
-        <v>10</v>
-      </c>
-      <c r="G111" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7">
-      <c r="A112" t="s">
+      <c r="C112" s="1" t="s">
         <v>267</v>
       </c>
       <c r="D112" t="s">
+        <v>8</v>
+      </c>
+      <c r="E112" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" t="s">
         <v>268</v>
       </c>
-      <c r="E112" s="1" t="s">
+      <c r="B113" t="s">
+        <v>266</v>
+      </c>
+      <c r="C113" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="F112" t="s">
-        <v>10</v>
-      </c>
-      <c r="G112" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
-      <c r="A113" t="s">
+      <c r="D113" t="s">
+        <v>8</v>
+      </c>
+      <c r="E113" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" t="s">
         <v>270</v>
       </c>
-      <c r="D113" t="s">
-        <v>268</v>
-      </c>
-      <c r="E113" s="1" t="s">
+      <c r="B114" t="s">
+        <v>266</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D114" t="s">
+        <v>66</v>
+      </c>
+      <c r="E114" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" t="s">
         <v>271</v>
       </c>
-      <c r="F113" t="s">
-        <v>10</v>
-      </c>
-      <c r="G113" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
-      <c r="A114" t="s">
+      <c r="B115" t="s">
         <v>272</v>
       </c>
-      <c r="D114" t="s">
-        <v>268</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="F114" t="s">
-        <v>68</v>
-      </c>
-      <c r="G114" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
-      <c r="A115" t="s">
+      <c r="C115" s="1" t="s">
         <v>273</v>
       </c>
       <c r="D115" t="s">
+        <v>8</v>
+      </c>
+      <c r="E115" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" t="s">
         <v>274</v>
       </c>
-      <c r="E115" s="1" t="s">
+      <c r="B116" t="s">
+        <v>272</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="F115" t="s">
-        <v>10</v>
-      </c>
-      <c r="G115" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7">
-      <c r="A116" t="s">
+      <c r="D116" t="s">
+        <v>8</v>
+      </c>
+      <c r="E116" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" t="s">
         <v>276</v>
       </c>
-      <c r="D116" t="s">
-        <v>274</v>
-      </c>
-      <c r="E116" s="1" t="s">
+      <c r="B117" t="s">
         <v>277</v>
       </c>
-      <c r="F116" t="s">
-        <v>10</v>
-      </c>
-      <c r="G116" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7">
-      <c r="A117" t="s">
+      <c r="C117" s="1" t="s">
         <v>278</v>
       </c>
       <c r="D117" t="s">
+        <v>8</v>
+      </c>
+      <c r="E117" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" t="s">
         <v>279</v>
       </c>
-      <c r="E117" s="1" t="s">
+      <c r="B118" t="s">
         <v>280</v>
       </c>
-      <c r="F117" t="s">
-        <v>10</v>
-      </c>
-      <c r="G117" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7">
-      <c r="A118" t="s">
+      <c r="C118" s="1" t="s">
         <v>281</v>
       </c>
       <c r="D118" t="s">
+        <v>8</v>
+      </c>
+      <c r="E118" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" t="s">
         <v>282</v>
       </c>
-      <c r="E118" s="1" t="s">
+      <c r="B119" t="s">
+        <v>280</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="F118" t="s">
-        <v>10</v>
-      </c>
-      <c r="G118" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7">
-      <c r="A119" t="s">
+      <c r="D119" t="s">
+        <v>8</v>
+      </c>
+      <c r="E119" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" t="s">
         <v>284</v>
       </c>
-      <c r="D119" t="s">
-        <v>282</v>
-      </c>
-      <c r="E119" s="1" t="s">
+      <c r="B120" t="s">
         <v>285</v>
       </c>
-      <c r="F119" t="s">
-        <v>10</v>
-      </c>
-      <c r="G119" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7">
-      <c r="A120" t="s">
+      <c r="C120" s="1" t="s">
         <v>286</v>
       </c>
       <c r="D120" t="s">
+        <v>66</v>
+      </c>
+      <c r="E120" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" t="s">
         <v>287</v>
       </c>
-      <c r="E120" s="1" t="s">
+      <c r="B121" t="s">
         <v>288</v>
       </c>
-      <c r="F120" t="s">
-        <v>68</v>
-      </c>
-      <c r="G120" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7">
-      <c r="A121" t="s">
+      <c r="C121" s="1" t="s">
         <v>289</v>
       </c>
       <c r="D121" t="s">
+        <v>8</v>
+      </c>
+      <c r="E121" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" t="s">
         <v>290</v>
       </c>
-      <c r="E121" s="1" t="s">
+      <c r="B122" t="s">
+        <v>288</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D122" t="s">
+        <v>8</v>
+      </c>
+      <c r="E122" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" t="s">
         <v>291</v>
       </c>
-      <c r="F121" t="s">
-        <v>10</v>
-      </c>
-      <c r="G121" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7">
-      <c r="A122" t="s">
+      <c r="B123" t="s">
         <v>292</v>
       </c>
-      <c r="D122" t="s">
-        <v>290</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F122" t="s">
-        <v>10</v>
-      </c>
-      <c r="G122" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7">
-      <c r="A123" t="s">
+      <c r="C123" s="1" t="s">
         <v>293</v>
       </c>
       <c r="D123" t="s">
+        <v>8</v>
+      </c>
+      <c r="E123" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" t="s">
         <v>294</v>
       </c>
-      <c r="E123" s="1" t="s">
+      <c r="B124" t="s">
         <v>295</v>
       </c>
-      <c r="F123" t="s">
-        <v>10</v>
-      </c>
-      <c r="G123" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7">
-      <c r="A124" t="s">
+      <c r="C124" s="1" t="s">
         <v>296</v>
       </c>
       <c r="D124" t="s">
+        <v>8</v>
+      </c>
+      <c r="E124" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" t="s">
         <v>297</v>
       </c>
-      <c r="E124" s="1" t="s">
+      <c r="B125" t="s">
         <v>298</v>
       </c>
-      <c r="F124" t="s">
-        <v>10</v>
-      </c>
-      <c r="G124" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7">
-      <c r="A125" t="s">
+      <c r="C125" s="1" t="s">
         <v>299</v>
       </c>
       <c r="D125" t="s">
+        <v>8</v>
+      </c>
+      <c r="E125" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" t="s">
         <v>300</v>
       </c>
-      <c r="E125" s="1" t="s">
+      <c r="B126" t="s">
+        <v>298</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="F125" t="s">
-        <v>10</v>
-      </c>
-      <c r="G125" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7">
-      <c r="A126" t="s">
+      <c r="D126" t="s">
+        <v>8</v>
+      </c>
+      <c r="E126" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" t="s">
         <v>302</v>
       </c>
-      <c r="D126" t="s">
-        <v>300</v>
-      </c>
-      <c r="E126" s="1" t="s">
+      <c r="B127" t="s">
         <v>303</v>
       </c>
-      <c r="F126" t="s">
-        <v>10</v>
-      </c>
-      <c r="G126" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7">
-      <c r="A127" t="s">
+      <c r="D127" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" t="s">
         <v>304</v>
       </c>
-      <c r="D127" t="s">
+      <c r="B128" t="s">
         <v>305</v>
       </c>
-      <c r="F127" t="s">
-        <v>10</v>
-      </c>
-      <c r="G127" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7">
-      <c r="A128" t="s">
+      <c r="C128" s="1" t="s">
         <v>306</v>
       </c>
       <c r="D128" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" t="s">
         <v>307</v>
       </c>
-      <c r="E128" s="1" t="s">
+      <c r="B129" t="s">
         <v>308</v>
       </c>
-      <c r="F128" t="s">
-        <v>10</v>
-      </c>
-      <c r="G128" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7">
-      <c r="A129" t="s">
+      <c r="C129" s="1" t="s">
         <v>309</v>
       </c>
       <c r="D129" t="s">
+        <v>66</v>
+      </c>
+      <c r="E129" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" t="s">
         <v>310</v>
       </c>
-      <c r="E129" s="1" t="s">
+      <c r="B130" t="s">
+        <v>308</v>
+      </c>
+      <c r="C130" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="F129" t="s">
-        <v>68</v>
-      </c>
-      <c r="G129" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7">
-      <c r="A130" t="s">
+      <c r="D130" t="s">
+        <v>66</v>
+      </c>
+      <c r="E130" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" t="s">
         <v>312</v>
       </c>
-      <c r="D130" t="s">
-        <v>310</v>
-      </c>
-      <c r="E130" s="1" t="s">
+      <c r="B131" t="s">
+        <v>308</v>
+      </c>
+      <c r="C131" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="F130" t="s">
-        <v>68</v>
-      </c>
-      <c r="G130" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7">
-      <c r="A131" t="s">
+      <c r="D131" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" t="s">
         <v>314</v>
       </c>
-      <c r="D131" t="s">
-        <v>310</v>
-      </c>
-      <c r="E131" s="1" t="s">
+      <c r="B132" t="s">
+        <v>308</v>
+      </c>
+      <c r="C132" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="F131" t="s">
-        <v>10</v>
-      </c>
-      <c r="G131" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7">
-      <c r="A132" t="s">
+      <c r="D132" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" t="s">
         <v>316</v>
       </c>
-      <c r="D132" t="s">
-        <v>310</v>
-      </c>
-      <c r="E132" s="1" t="s">
+      <c r="B133" t="s">
         <v>317</v>
       </c>
-      <c r="F132" t="s">
-        <v>10</v>
-      </c>
-      <c r="G132" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7">
-      <c r="A133" t="s">
+      <c r="C133" s="1" t="s">
         <v>318</v>
       </c>
       <c r="D133" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" t="s">
         <v>319</v>
       </c>
-      <c r="E133" s="1" t="s">
+      <c r="B134" t="s">
+        <v>317</v>
+      </c>
+      <c r="C134" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="F133" t="s">
-        <v>10</v>
-      </c>
-      <c r="G133" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7">
-      <c r="A134" t="s">
+      <c r="D134" t="s">
+        <v>8</v>
+      </c>
+      <c r="E134" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" t="s">
         <v>321</v>
       </c>
-      <c r="D134" t="s">
-        <v>319</v>
-      </c>
-      <c r="E134" s="1" t="s">
+      <c r="B135" t="s">
         <v>322</v>
       </c>
-      <c r="F134" t="s">
-        <v>10</v>
-      </c>
-      <c r="G134" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7">
-      <c r="A135" t="s">
+      <c r="C135" s="1" t="s">
         <v>323</v>
       </c>
       <c r="D135" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" t="s">
         <v>324</v>
       </c>
-      <c r="E135" s="1" t="s">
+      <c r="B136" t="s">
         <v>325</v>
       </c>
-      <c r="F135" t="s">
-        <v>10</v>
-      </c>
-      <c r="G135" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7">
-      <c r="A136" t="s">
+      <c r="C136" s="1" t="s">
         <v>326</v>
       </c>
       <c r="D136" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" t="s">
         <v>327</v>
       </c>
-      <c r="E136" s="1" t="s">
+      <c r="B137" t="s">
+        <v>325</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="F136" t="s">
-        <v>10</v>
-      </c>
-      <c r="G136" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7">
-      <c r="A137" t="s">
+      <c r="D137" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" t="s">
         <v>329</v>
       </c>
-      <c r="D137" t="s">
-        <v>327</v>
-      </c>
-      <c r="E137" s="1" t="s">
+      <c r="B138" t="s">
+        <v>325</v>
+      </c>
+      <c r="C138" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="F137" t="s">
-        <v>10</v>
-      </c>
-      <c r="G137" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7">
-      <c r="A138" t="s">
+      <c r="D138" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" t="s">
         <v>331</v>
       </c>
-      <c r="D138" t="s">
-        <v>327</v>
-      </c>
-      <c r="E138" s="1" t="s">
+      <c r="B139" t="s">
         <v>332</v>
       </c>
-      <c r="F138" t="s">
-        <v>10</v>
-      </c>
-      <c r="G138" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7">
-      <c r="A139" t="s">
+      <c r="C139" s="1" t="s">
         <v>333</v>
       </c>
       <c r="D139" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" t="s">
         <v>334</v>
       </c>
-      <c r="E139" s="1" t="s">
+      <c r="B140" t="s">
+        <v>332</v>
+      </c>
+      <c r="C140" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="F139" t="s">
-        <v>10</v>
-      </c>
-      <c r="G139" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7">
-      <c r="A140" t="s">
+      <c r="D140" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" t="s">
         <v>336</v>
       </c>
-      <c r="D140" t="s">
-        <v>334</v>
-      </c>
-      <c r="E140" s="1" t="s">
+      <c r="B141" t="s">
         <v>337</v>
       </c>
-      <c r="F140" t="s">
-        <v>10</v>
-      </c>
-      <c r="G140" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7">
-      <c r="A141" t="s">
+      <c r="C141" s="1" t="s">
         <v>338</v>
       </c>
       <c r="D141" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" t="s">
         <v>339</v>
       </c>
-      <c r="E141" s="1" t="s">
+      <c r="B142" t="s">
+        <v>337</v>
+      </c>
+      <c r="C142" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="F141" t="s">
-        <v>10</v>
-      </c>
-      <c r="G141" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7">
-      <c r="A142" t="s">
+      <c r="D142" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" t="s">
         <v>341</v>
       </c>
-      <c r="D142" t="s">
-        <v>339</v>
-      </c>
-      <c r="E142" s="1" t="s">
+      <c r="B143" t="s">
         <v>342</v>
       </c>
-      <c r="F142" t="s">
-        <v>10</v>
-      </c>
-      <c r="G142" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7">
-      <c r="A143" t="s">
+      <c r="C143" s="1" t="s">
         <v>343</v>
       </c>
       <c r="D143" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" t="s">
         <v>344</v>
       </c>
-      <c r="E143" s="1" t="s">
+      <c r="B144" t="s">
         <v>345</v>
       </c>
-      <c r="F143" t="s">
-        <v>10</v>
-      </c>
-      <c r="G143" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7">
-      <c r="A144" t="s">
+      <c r="C144" s="1" t="s">
         <v>346</v>
       </c>
       <c r="D144" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" t="s">
         <v>347</v>
       </c>
-      <c r="E144" s="1" t="s">
+      <c r="B145" t="s">
+        <v>345</v>
+      </c>
+      <c r="C145" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="F144" t="s">
-        <v>10</v>
-      </c>
-      <c r="G144" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7">
-      <c r="A145" t="s">
+      <c r="D145" t="s">
+        <v>8</v>
+      </c>
+      <c r="E145" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" t="s">
         <v>349</v>
       </c>
-      <c r="D145" t="s">
-        <v>347</v>
-      </c>
-      <c r="E145" s="1" t="s">
+      <c r="B146" t="s">
         <v>350</v>
       </c>
-      <c r="F145" t="s">
-        <v>10</v>
-      </c>
-      <c r="G145" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7">
-      <c r="A146" t="s">
+      <c r="C146" s="1" t="s">
         <v>351</v>
       </c>
       <c r="D146" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" t="s">
         <v>352</v>
       </c>
-      <c r="E146" s="1" t="s">
+      <c r="B147" t="s">
         <v>353</v>
       </c>
-      <c r="F146" t="s">
-        <v>10</v>
-      </c>
-      <c r="G146" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7">
-      <c r="A147" t="s">
+      <c r="C147" s="1" t="s">
         <v>354</v>
       </c>
       <c r="D147" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" t="s">
         <v>355</v>
       </c>
-      <c r="E147" s="1" t="s">
+      <c r="B148" t="s">
         <v>356</v>
       </c>
-      <c r="F147" t="s">
-        <v>10</v>
-      </c>
-      <c r="G147" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7">
-      <c r="A148" t="s">
+      <c r="C148" s="1" t="s">
         <v>357</v>
       </c>
       <c r="D148" t="s">
+        <v>66</v>
+      </c>
+      <c r="E148" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" t="s">
         <v>358</v>
       </c>
-      <c r="E148" s="1" t="s">
+      <c r="B149" t="s">
+        <v>356</v>
+      </c>
+      <c r="C149" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="F148" t="s">
-        <v>68</v>
-      </c>
-      <c r="G148" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7">
-      <c r="A149" t="s">
+      <c r="D149" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" t="s">
         <v>360</v>
       </c>
-      <c r="D149" t="s">
-        <v>358</v>
-      </c>
-      <c r="E149" s="1" t="s">
+      <c r="B150" t="s">
         <v>361</v>
       </c>
-      <c r="F149" t="s">
-        <v>10</v>
-      </c>
-      <c r="G149" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7">
-      <c r="A150" t="s">
+      <c r="C150" s="1" t="s">
         <v>362</v>
       </c>
       <c r="D150" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" t="s">
         <v>363</v>
       </c>
-      <c r="E150" s="1" t="s">
+      <c r="B151" t="s">
+        <v>361</v>
+      </c>
+      <c r="C151" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="F150" t="s">
-        <v>10</v>
-      </c>
-      <c r="G150" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7">
-      <c r="A151" t="s">
+      <c r="D151" t="s">
+        <v>8</v>
+      </c>
+      <c r="E151" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" t="s">
         <v>365</v>
       </c>
-      <c r="D151" t="s">
-        <v>363</v>
-      </c>
-      <c r="E151" s="1" t="s">
+      <c r="B152" t="s">
+        <v>361</v>
+      </c>
+      <c r="C152" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="F151" t="s">
-        <v>10</v>
-      </c>
-      <c r="G151" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7">
-      <c r="A152" t="s">
+      <c r="D152" t="s">
+        <v>8</v>
+      </c>
+      <c r="E152" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" t="s">
         <v>367</v>
       </c>
-      <c r="D152" t="s">
-        <v>363</v>
-      </c>
-      <c r="E152" s="1" t="s">
+      <c r="B153" t="s">
         <v>368</v>
       </c>
-      <c r="F152" t="s">
-        <v>10</v>
-      </c>
-      <c r="G152" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7">
-      <c r="A153" t="s">
+      <c r="C153" s="1" t="s">
         <v>369</v>
       </c>
       <c r="D153" t="s">
+        <v>8</v>
+      </c>
+      <c r="E153" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" t="s">
         <v>370</v>
       </c>
-      <c r="E153" s="1" t="s">
+      <c r="B154" t="s">
         <v>371</v>
       </c>
-      <c r="F153" t="s">
-        <v>10</v>
-      </c>
-      <c r="G153" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7">
-      <c r="A154" t="s">
+      <c r="C154" s="1" t="s">
         <v>372</v>
       </c>
       <c r="D154" t="s">
+        <v>8</v>
+      </c>
+      <c r="E154" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" t="s">
         <v>373</v>
       </c>
-      <c r="E154" s="1" t="s">
+      <c r="B155" t="s">
         <v>374</v>
       </c>
-      <c r="F154" t="s">
-        <v>10</v>
-      </c>
-      <c r="G154" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7">
-      <c r="A155" t="s">
+      <c r="C155" s="1" t="s">
         <v>375</v>
       </c>
       <c r="D155" t="s">
+        <v>8</v>
+      </c>
+      <c r="E155" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" t="s">
         <v>376</v>
       </c>
-      <c r="E155" s="1" t="s">
+      <c r="B156" t="s">
+        <v>374</v>
+      </c>
+      <c r="C156" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="F155" t="s">
-        <v>10</v>
-      </c>
-      <c r="G155" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7">
-      <c r="A156" t="s">
+      <c r="D156" t="s">
+        <v>8</v>
+      </c>
+      <c r="E156" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" t="s">
         <v>378</v>
       </c>
-      <c r="D156" t="s">
-        <v>376</v>
-      </c>
-      <c r="E156" s="1" t="s">
+      <c r="B157" t="s">
         <v>379</v>
       </c>
-      <c r="F156" t="s">
-        <v>10</v>
-      </c>
-      <c r="G156" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7">
-      <c r="A157" t="s">
+      <c r="C157" s="1" t="s">
         <v>380</v>
       </c>
       <c r="D157" t="s">
+        <v>8</v>
+      </c>
+      <c r="E157" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" t="s">
         <v>381</v>
       </c>
-      <c r="E157" s="1" t="s">
+      <c r="B158" t="s">
         <v>382</v>
       </c>
-      <c r="F157" t="s">
-        <v>10</v>
-      </c>
-      <c r="G157" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7">
-      <c r="A158" t="s">
+      <c r="C158" s="1" t="s">
         <v>383</v>
       </c>
       <c r="D158" t="s">
+        <v>8</v>
+      </c>
+      <c r="E158" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" t="s">
         <v>384</v>
       </c>
-      <c r="E158" s="1" t="s">
+      <c r="B159" t="s">
+        <v>382</v>
+      </c>
+      <c r="C159" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="F158" t="s">
-        <v>10</v>
-      </c>
-      <c r="G158" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7">
-      <c r="A159" t="s">
+      <c r="D159" t="s">
+        <v>8</v>
+      </c>
+      <c r="E159" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" t="s">
         <v>386</v>
       </c>
-      <c r="D159" t="s">
-        <v>384</v>
-      </c>
-      <c r="E159" s="1" t="s">
+      <c r="B160" t="s">
         <v>387</v>
       </c>
-      <c r="F159" t="s">
-        <v>10</v>
-      </c>
-      <c r="G159" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7">
-      <c r="A160" t="s">
+      <c r="C160" s="1" t="s">
         <v>388</v>
       </c>
       <c r="D160" t="s">
+        <v>8</v>
+      </c>
+      <c r="E160" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" t="s">
         <v>389</v>
       </c>
-      <c r="E160" s="1" t="s">
+      <c r="B161" t="s">
+        <v>387</v>
+      </c>
+      <c r="C161" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="F160" t="s">
-        <v>10</v>
-      </c>
-      <c r="G160" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7">
-      <c r="A161" t="s">
+      <c r="D161" t="s">
+        <v>8</v>
+      </c>
+      <c r="E161" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" t="s">
         <v>391</v>
       </c>
-      <c r="D161" t="s">
-        <v>389</v>
-      </c>
-      <c r="E161" s="1" t="s">
+      <c r="B162" t="s">
         <v>392</v>
       </c>
-      <c r="F161" t="s">
-        <v>10</v>
-      </c>
-      <c r="G161" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7">
-      <c r="A162" t="s">
+      <c r="C162" s="1" t="s">
         <v>393</v>
       </c>
       <c r="D162" t="s">
+        <v>66</v>
+      </c>
+      <c r="E162" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" t="s">
         <v>394</v>
       </c>
-      <c r="E162" s="1" t="s">
+      <c r="B163" t="s">
+        <v>392</v>
+      </c>
+      <c r="C163" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="F162" t="s">
-        <v>68</v>
-      </c>
-      <c r="G162" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7">
-      <c r="A163" t="s">
+      <c r="D163" t="s">
+        <v>66</v>
+      </c>
+      <c r="E163" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" t="s">
         <v>396</v>
       </c>
-      <c r="D163" t="s">
-        <v>394</v>
-      </c>
-      <c r="E163" s="1" t="s">
+      <c r="B164" t="s">
+        <v>392</v>
+      </c>
+      <c r="C164" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="F163" t="s">
-        <v>68</v>
-      </c>
-      <c r="G163" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7">
-      <c r="A164" t="s">
+      <c r="D164" t="s">
+        <v>8</v>
+      </c>
+      <c r="E164" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" t="s">
         <v>398</v>
       </c>
-      <c r="D164" t="s">
-        <v>394</v>
-      </c>
-      <c r="E164" s="1" t="s">
+      <c r="B165" t="s">
         <v>399</v>
       </c>
-      <c r="F164" t="s">
-        <v>10</v>
-      </c>
-      <c r="G164" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7">
-      <c r="A165" t="s">
+      <c r="C165" s="1" t="s">
         <v>400</v>
       </c>
       <c r="D165" t="s">
+        <v>8</v>
+      </c>
+      <c r="E165" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" t="s">
         <v>401</v>
       </c>
-      <c r="E165" s="1" t="s">
+      <c r="B166" t="s">
         <v>402</v>
       </c>
-      <c r="F165" t="s">
-        <v>10</v>
-      </c>
-      <c r="G165" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7">
-      <c r="A166" t="s">
+      <c r="C166" s="1" t="s">
         <v>403</v>
       </c>
       <c r="D166" t="s">
+        <v>8</v>
+      </c>
+      <c r="E166" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" t="s">
         <v>404</v>
       </c>
-      <c r="E166" s="1" t="s">
+      <c r="B167" t="s">
+        <v>402</v>
+      </c>
+      <c r="C167" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="F166" t="s">
-        <v>10</v>
-      </c>
-      <c r="G166" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7">
-      <c r="A167" t="s">
+      <c r="D167" t="s">
+        <v>8</v>
+      </c>
+      <c r="E167" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" t="s">
         <v>406</v>
       </c>
-      <c r="D167" t="s">
-        <v>404</v>
-      </c>
-      <c r="E167" s="1" t="s">
+      <c r="B168" t="s">
         <v>407</v>
       </c>
-      <c r="F167" t="s">
-        <v>10</v>
-      </c>
-      <c r="G167" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7">
-      <c r="A168" t="s">
+      <c r="C168" s="1" t="s">
         <v>408</v>
       </c>
       <c r="D168" t="s">
+        <v>8</v>
+      </c>
+      <c r="E168" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" t="s">
         <v>409</v>
       </c>
-      <c r="E168" s="1" t="s">
+      <c r="B169" t="s">
+        <v>407</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D169" t="s">
+        <v>66</v>
+      </c>
+      <c r="E169" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" t="s">
         <v>410</v>
       </c>
-      <c r="F168" t="s">
-        <v>10</v>
-      </c>
-      <c r="G168" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7">
-      <c r="A169" t="s">
+      <c r="B170" t="s">
         <v>411</v>
       </c>
-      <c r="D169" t="s">
-        <v>409</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="F169" t="s">
-        <v>68</v>
-      </c>
-      <c r="G169" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7">
-      <c r="A170" t="s">
+      <c r="C170" s="1" t="s">
         <v>412</v>
       </c>
       <c r="D170" t="s">
+        <v>8</v>
+      </c>
+      <c r="E170" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" t="s">
         <v>413</v>
       </c>
-      <c r="E170" s="1" t="s">
+      <c r="B171" t="s">
         <v>414</v>
       </c>
-      <c r="F170" t="s">
-        <v>10</v>
-      </c>
-      <c r="G170" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7">
-      <c r="A171" t="s">
+      <c r="D171" t="s">
+        <v>8</v>
+      </c>
+      <c r="E171" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" t="s">
         <v>415</v>
       </c>
-      <c r="D171" t="s">
+      <c r="B172" t="s">
         <v>416</v>
       </c>
-      <c r="F171" t="s">
-        <v>10</v>
-      </c>
-      <c r="G171" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7">
-      <c r="A172" t="s">
+      <c r="C172" s="1" t="s">
         <v>417</v>
       </c>
       <c r="D172" t="s">
+        <v>8</v>
+      </c>
+      <c r="E172" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" t="s">
         <v>418</v>
       </c>
-      <c r="E172" s="1" t="s">
+      <c r="B173" t="s">
+        <v>416</v>
+      </c>
+      <c r="C173" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="F172" t="s">
-        <v>10</v>
-      </c>
-      <c r="G172" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7">
-      <c r="A173" t="s">
+      <c r="D173" t="s">
+        <v>8</v>
+      </c>
+      <c r="E173" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" t="s">
         <v>420</v>
       </c>
-      <c r="D173" t="s">
-        <v>418</v>
-      </c>
-      <c r="E173" s="1" t="s">
+      <c r="B174" t="s">
         <v>421</v>
       </c>
-      <c r="F173" t="s">
-        <v>10</v>
-      </c>
-      <c r="G173" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7">
-      <c r="A174" t="s">
+      <c r="C174" s="1" t="s">
         <v>422</v>
       </c>
       <c r="D174" t="s">
+        <v>8</v>
+      </c>
+      <c r="E174" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" t="s">
         <v>423</v>
       </c>
-      <c r="E174" s="1" t="s">
+      <c r="B175" t="s">
+        <v>421</v>
+      </c>
+      <c r="C175" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="F174" t="s">
-        <v>10</v>
-      </c>
-      <c r="G174" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7">
-      <c r="A175" t="s">
+      <c r="D175" t="s">
+        <v>8</v>
+      </c>
+      <c r="E175" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" t="s">
         <v>425</v>
       </c>
-      <c r="D175" t="s">
-        <v>423</v>
-      </c>
-      <c r="E175" s="1" t="s">
+      <c r="B176" t="s">
         <v>426</v>
       </c>
-      <c r="F175" t="s">
-        <v>10</v>
-      </c>
-      <c r="G175" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7">
-      <c r="A176" t="s">
+      <c r="C176" s="1" t="s">
         <v>427</v>
       </c>
       <c r="D176" t="s">
+        <v>8</v>
+      </c>
+      <c r="E176" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" t="s">
         <v>428</v>
       </c>
-      <c r="E176" s="1" t="s">
+      <c r="B177" t="s">
         <v>429</v>
       </c>
-      <c r="F176" t="s">
-        <v>10</v>
-      </c>
-      <c r="G176" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7">
-      <c r="A177" t="s">
+      <c r="C177" s="1" t="s">
         <v>430</v>
       </c>
       <c r="D177" t="s">
+        <v>8</v>
+      </c>
+      <c r="E177" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" t="s">
         <v>431</v>
       </c>
-      <c r="E177" s="1" t="s">
+      <c r="B178" t="s">
+        <v>429</v>
+      </c>
+      <c r="C178" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="F177" t="s">
-        <v>10</v>
-      </c>
-      <c r="G177" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7">
-      <c r="A178" t="s">
+      <c r="D178" t="s">
+        <v>8</v>
+      </c>
+      <c r="E178" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" t="s">
         <v>433</v>
       </c>
-      <c r="D178" t="s">
-        <v>431</v>
-      </c>
-      <c r="E178" s="1" t="s">
+      <c r="B179" t="s">
         <v>434</v>
       </c>
-      <c r="F178" t="s">
-        <v>10</v>
-      </c>
-      <c r="G178" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7">
-      <c r="A179" t="s">
+      <c r="C179" s="1" t="s">
         <v>435</v>
       </c>
       <c r="D179" t="s">
+        <v>66</v>
+      </c>
+      <c r="E179" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" t="s">
         <v>436</v>
       </c>
-      <c r="E179" s="1" t="s">
+      <c r="B180" t="s">
+        <v>434</v>
+      </c>
+      <c r="C180" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="F179" t="s">
-        <v>68</v>
-      </c>
-      <c r="G179" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7">
-      <c r="A180" t="s">
+      <c r="D180" t="s">
+        <v>8</v>
+      </c>
+      <c r="E180" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" t="s">
         <v>438</v>
       </c>
-      <c r="D180" t="s">
-        <v>436</v>
-      </c>
-      <c r="E180" s="1" t="s">
+      <c r="B181" t="s">
+        <v>434</v>
+      </c>
+      <c r="C181" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="F180" t="s">
-        <v>10</v>
-      </c>
-      <c r="G180" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7">
-      <c r="A181" t="s">
+      <c r="D181" t="s">
+        <v>8</v>
+      </c>
+      <c r="E181" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" t="s">
         <v>440</v>
       </c>
-      <c r="D181" t="s">
-        <v>436</v>
-      </c>
-      <c r="E181" s="1" t="s">
+      <c r="B182" t="s">
         <v>441</v>
       </c>
-      <c r="F181" t="s">
-        <v>10</v>
-      </c>
-      <c r="G181" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7">
-      <c r="A182" t="s">
+      <c r="C182" s="1" t="s">
         <v>442</v>
       </c>
       <c r="D182" t="s">
+        <v>8</v>
+      </c>
+      <c r="E182" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" t="s">
         <v>443</v>
       </c>
-      <c r="E182" s="1" t="s">
+      <c r="B183" t="s">
         <v>444</v>
       </c>
-      <c r="F182" t="s">
-        <v>10</v>
-      </c>
-      <c r="G182" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7">
-      <c r="A183" t="s">
+      <c r="D183" t="s">
+        <v>8</v>
+      </c>
+      <c r="E183" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" t="s">
         <v>445</v>
       </c>
-      <c r="D183" t="s">
+      <c r="B184" t="s">
         <v>446</v>
       </c>
-      <c r="F183" t="s">
-        <v>10</v>
-      </c>
-      <c r="G183" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7">
-      <c r="A184" t="s">
+      <c r="C184" s="1" t="s">
         <v>447</v>
       </c>
       <c r="D184" t="s">
+        <v>8</v>
+      </c>
+      <c r="E184" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" t="s">
         <v>448</v>
       </c>
-      <c r="E184" s="1" t="s">
+      <c r="B185" t="s">
+        <v>444</v>
+      </c>
+      <c r="C185" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="F184" t="s">
-        <v>10</v>
-      </c>
-      <c r="G184" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7">
-      <c r="A185" t="s">
+      <c r="D185" t="s">
+        <v>8</v>
+      </c>
+      <c r="E185" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" t="s">
         <v>450</v>
       </c>
-      <c r="D185" t="s">
+      <c r="B186" t="s">
+        <v>444</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D186" t="s">
+        <v>8</v>
+      </c>
+      <c r="E186" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" t="s">
+        <v>452</v>
+      </c>
+      <c r="B187" t="s">
+        <v>453</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="D187" t="s">
+        <v>8</v>
+      </c>
+      <c r="E187" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" t="s">
+        <v>455</v>
+      </c>
+      <c r="B188" t="s">
         <v>446</v>
       </c>
-      <c r="E185" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="F185" t="s">
-        <v>10</v>
-      </c>
-      <c r="G185" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7">
-      <c r="A186" t="s">
-        <v>452</v>
-      </c>
-      <c r="D186" t="s">
+      <c r="C188" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="D188" t="s">
+        <v>8</v>
+      </c>
+      <c r="E188" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" t="s">
+        <v>457</v>
+      </c>
+      <c r="B189" t="s">
         <v>446</v>
       </c>
-      <c r="E186" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="F186" t="s">
-        <v>10</v>
-      </c>
-      <c r="G186" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7">
-      <c r="A187" t="s">
-        <v>454</v>
-      </c>
-      <c r="D187" t="s">
-        <v>455</v>
-      </c>
-      <c r="E187" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="F187" t="s">
-        <v>10</v>
-      </c>
-      <c r="G187" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7">
-      <c r="A188" t="s">
-        <v>457</v>
-      </c>
-      <c r="D188" t="s">
-        <v>448</v>
-      </c>
-      <c r="E188" s="1" t="s">
+      <c r="C189" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="F188" t="s">
-        <v>10</v>
-      </c>
-      <c r="G188" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7">
-      <c r="A189" t="s">
+      <c r="D189" t="s">
+        <v>8</v>
+      </c>
+      <c r="E189" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" t="s">
         <v>459</v>
       </c>
-      <c r="D189" t="s">
-        <v>448</v>
-      </c>
-      <c r="E189" s="1" t="s">
+      <c r="B190" t="s">
+        <v>444</v>
+      </c>
+      <c r="C190" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="F189" t="s">
-        <v>10</v>
-      </c>
-      <c r="G189" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7">
-      <c r="A190" t="s">
+      <c r="D190" t="s">
+        <v>8</v>
+      </c>
+      <c r="E190" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" t="s">
         <v>461</v>
       </c>
-      <c r="D190" t="s">
-        <v>446</v>
-      </c>
-      <c r="E190" s="1" t="s">
+      <c r="B191" t="s">
+        <v>444</v>
+      </c>
+      <c r="C191" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="F190" t="s">
-        <v>10</v>
-      </c>
-      <c r="G190" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7">
-      <c r="A191" t="s">
+      <c r="D191" t="s">
+        <v>8</v>
+      </c>
+      <c r="E191" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" t="s">
         <v>463</v>
       </c>
-      <c r="D191" t="s">
-        <v>446</v>
-      </c>
-      <c r="E191" s="1" t="s">
+      <c r="B192" t="s">
+        <v>212</v>
+      </c>
+      <c r="C192" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="F191" t="s">
-        <v>10</v>
-      </c>
-      <c r="G191" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7">
-      <c r="A192" t="s">
+      <c r="D192" t="s">
+        <v>8</v>
+      </c>
+      <c r="E192" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" t="s">
         <v>465</v>
       </c>
-      <c r="D192" t="s">
-        <v>214</v>
-      </c>
-      <c r="E192" s="1" t="s">
+      <c r="B193" t="s">
         <v>466</v>
       </c>
-      <c r="F192" t="s">
-        <v>10</v>
-      </c>
-      <c r="G192" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7">
-      <c r="A193" t="s">
+      <c r="C193" s="1" t="s">
         <v>467</v>
       </c>
       <c r="D193" t="s">
+        <v>8</v>
+      </c>
+      <c r="E193" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" t="s">
         <v>468</v>
       </c>
-      <c r="E193" s="1" t="s">
+      <c r="B194" t="s">
+        <v>466</v>
+      </c>
+      <c r="C194" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="F193" t="s">
-        <v>10</v>
-      </c>
-      <c r="G193" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7">
-      <c r="A194" t="s">
+      <c r="D194" t="s">
+        <v>8</v>
+      </c>
+      <c r="E194" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" t="s">
         <v>470</v>
       </c>
-      <c r="D194" t="s">
-        <v>468</v>
-      </c>
-      <c r="E194" s="1" t="s">
+      <c r="B195" t="s">
+        <v>466</v>
+      </c>
+      <c r="C195" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="F194" t="s">
-        <v>10</v>
-      </c>
-      <c r="G194" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7">
-      <c r="A195" t="s">
+      <c r="D195" t="s">
+        <v>66</v>
+      </c>
+      <c r="E195" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" t="s">
         <v>472</v>
       </c>
-      <c r="D195" t="s">
-        <v>468</v>
-      </c>
-      <c r="E195" s="1" t="s">
+      <c r="B196" t="s">
         <v>473</v>
       </c>
-      <c r="F195" t="s">
-        <v>68</v>
-      </c>
-      <c r="G195" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7">
-      <c r="A196" t="s">
+      <c r="C196" s="1" t="s">
         <v>474</v>
       </c>
       <c r="D196" t="s">
+        <v>8</v>
+      </c>
+      <c r="E196" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" t="s">
         <v>475</v>
       </c>
-      <c r="E196" s="1" t="s">
+      <c r="B197" t="s">
         <v>476</v>
       </c>
-      <c r="F196" t="s">
-        <v>10</v>
-      </c>
-      <c r="G196" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7">
-      <c r="A197" t="s">
+      <c r="D197" t="s">
+        <v>8</v>
+      </c>
+      <c r="E197" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" t="s">
         <v>477</v>
       </c>
-      <c r="D197" t="s">
+      <c r="B198" t="s">
+        <v>476</v>
+      </c>
+      <c r="C198" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="F197" t="s">
-        <v>10</v>
-      </c>
-      <c r="G197" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7">
-      <c r="A198" t="s">
-        <v>479</v>
-      </c>
       <c r="D198" t="s">
-        <v>478</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="F198" t="s">
-        <v>10</v>
-      </c>
-      <c r="G198" t="b">
+        <v>8</v>
+      </c>
+      <c r="E198" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E21" r:id="rId19"/>
-    <hyperlink ref="E22" r:id="rId20"/>
-    <hyperlink ref="E23" r:id="rId21"/>
-    <hyperlink ref="E24" r:id="rId22"/>
-    <hyperlink ref="E25" r:id="rId23"/>
-    <hyperlink ref="E26" r:id="rId24"/>
-    <hyperlink ref="E27" r:id="rId25"/>
-    <hyperlink ref="E28" r:id="rId26"/>
-    <hyperlink ref="E29" r:id="rId27"/>
-    <hyperlink ref="E30" r:id="rId28"/>
-    <hyperlink ref="E31" r:id="rId29"/>
-    <hyperlink ref="E32" r:id="rId30"/>
-    <hyperlink ref="E33" r:id="rId31"/>
-    <hyperlink ref="E34" r:id="rId32"/>
-    <hyperlink ref="E35" r:id="rId33"/>
-    <hyperlink ref="E36" r:id="rId34"/>
-    <hyperlink ref="E37" r:id="rId35"/>
-    <hyperlink ref="E38" r:id="rId36"/>
-    <hyperlink ref="E39" r:id="rId37"/>
-    <hyperlink ref="E40" r:id="rId38"/>
-    <hyperlink ref="E41" r:id="rId39"/>
-    <hyperlink ref="E42" r:id="rId40"/>
-    <hyperlink ref="E43" r:id="rId41"/>
-    <hyperlink ref="E44" r:id="rId42"/>
-    <hyperlink ref="E45" r:id="rId43"/>
-    <hyperlink ref="E46" r:id="rId44"/>
-    <hyperlink ref="E47" r:id="rId45"/>
-    <hyperlink ref="E48" r:id="rId46"/>
-    <hyperlink ref="E49" r:id="rId47"/>
-    <hyperlink ref="E50" r:id="rId48"/>
-    <hyperlink ref="E51" r:id="rId49"/>
-    <hyperlink ref="E52" r:id="rId50"/>
-    <hyperlink ref="E53" r:id="rId51"/>
-    <hyperlink ref="E54" r:id="rId52"/>
-    <hyperlink ref="E55" r:id="rId53"/>
-    <hyperlink ref="E56" r:id="rId54"/>
-    <hyperlink ref="E57" r:id="rId55"/>
-    <hyperlink ref="E58" r:id="rId56"/>
-    <hyperlink ref="E59" r:id="rId57"/>
-    <hyperlink ref="E60" r:id="rId58"/>
-    <hyperlink ref="E61" r:id="rId59"/>
-    <hyperlink ref="E62" r:id="rId60"/>
-    <hyperlink ref="E63" r:id="rId61"/>
-    <hyperlink ref="E64" r:id="rId62"/>
-    <hyperlink ref="E65" r:id="rId63"/>
-    <hyperlink ref="E66" r:id="rId64"/>
-    <hyperlink ref="E67" r:id="rId65"/>
-    <hyperlink ref="E68" r:id="rId66"/>
-    <hyperlink ref="E69" r:id="rId67"/>
-    <hyperlink ref="E70" r:id="rId68"/>
-    <hyperlink ref="E71" r:id="rId69"/>
-    <hyperlink ref="E72" r:id="rId70"/>
-    <hyperlink ref="E73" r:id="rId71"/>
-    <hyperlink ref="E74" r:id="rId72"/>
-    <hyperlink ref="E75" r:id="rId73"/>
-    <hyperlink ref="E76" r:id="rId74"/>
-    <hyperlink ref="E77" r:id="rId75"/>
-    <hyperlink ref="E78" r:id="rId76"/>
-    <hyperlink ref="E79" r:id="rId77"/>
-    <hyperlink ref="E80" r:id="rId78"/>
-    <hyperlink ref="E81" r:id="rId79"/>
-    <hyperlink ref="E82" r:id="rId80"/>
-    <hyperlink ref="E83" r:id="rId81"/>
-    <hyperlink ref="E84" r:id="rId82"/>
-    <hyperlink ref="E85" r:id="rId83"/>
-    <hyperlink ref="E86" r:id="rId84"/>
-    <hyperlink ref="E87" r:id="rId85"/>
-    <hyperlink ref="E88" r:id="rId86"/>
-    <hyperlink ref="E89" r:id="rId87"/>
-    <hyperlink ref="E90" r:id="rId88"/>
-    <hyperlink ref="E91" r:id="rId89"/>
-    <hyperlink ref="E92" r:id="rId90"/>
-    <hyperlink ref="E93" r:id="rId91"/>
-    <hyperlink ref="E94" r:id="rId92"/>
-    <hyperlink ref="E95" r:id="rId93"/>
-    <hyperlink ref="E96" r:id="rId94"/>
-    <hyperlink ref="E97" r:id="rId95"/>
-    <hyperlink ref="E98" r:id="rId96"/>
-    <hyperlink ref="E99" r:id="rId97"/>
-    <hyperlink ref="E100" r:id="rId98"/>
-    <hyperlink ref="E101" r:id="rId99"/>
-    <hyperlink ref="E102" r:id="rId100"/>
-    <hyperlink ref="E103" r:id="rId101"/>
-    <hyperlink ref="E104" r:id="rId102"/>
-    <hyperlink ref="E105" r:id="rId103"/>
-    <hyperlink ref="E106" r:id="rId104"/>
-    <hyperlink ref="E107" r:id="rId105"/>
-    <hyperlink ref="E108" r:id="rId106"/>
-    <hyperlink ref="E109" r:id="rId107"/>
-    <hyperlink ref="E110" r:id="rId108"/>
-    <hyperlink ref="E111" r:id="rId109"/>
-    <hyperlink ref="E112" r:id="rId110"/>
-    <hyperlink ref="E113" r:id="rId111"/>
-    <hyperlink ref="E114" r:id="rId112"/>
-    <hyperlink ref="E115" r:id="rId113"/>
-    <hyperlink ref="E116" r:id="rId114"/>
-    <hyperlink ref="E117" r:id="rId115"/>
-    <hyperlink ref="E118" r:id="rId116"/>
-    <hyperlink ref="E119" r:id="rId117"/>
-    <hyperlink ref="E120" r:id="rId118"/>
-    <hyperlink ref="E121" r:id="rId119"/>
-    <hyperlink ref="E122" r:id="rId120"/>
-    <hyperlink ref="E123" r:id="rId121"/>
-    <hyperlink ref="E124" r:id="rId122"/>
-    <hyperlink ref="E125" r:id="rId123"/>
-    <hyperlink ref="E126" r:id="rId124"/>
-    <hyperlink ref="E128" r:id="rId125"/>
-    <hyperlink ref="E129" r:id="rId126"/>
-    <hyperlink ref="E130" r:id="rId127"/>
-    <hyperlink ref="E131" r:id="rId128"/>
-    <hyperlink ref="E132" r:id="rId129"/>
-    <hyperlink ref="E133" r:id="rId130"/>
-    <hyperlink ref="E134" r:id="rId131"/>
-    <hyperlink ref="E135" r:id="rId132"/>
-    <hyperlink ref="E136" r:id="rId133"/>
-    <hyperlink ref="E137" r:id="rId134"/>
-    <hyperlink ref="E138" r:id="rId135"/>
-    <hyperlink ref="E139" r:id="rId136"/>
-    <hyperlink ref="E140" r:id="rId137"/>
-    <hyperlink ref="E141" r:id="rId138"/>
-    <hyperlink ref="E142" r:id="rId139"/>
-    <hyperlink ref="E143" r:id="rId140"/>
-    <hyperlink ref="E144" r:id="rId141"/>
-    <hyperlink ref="E145" r:id="rId142"/>
-    <hyperlink ref="E146" r:id="rId143"/>
-    <hyperlink ref="E147" r:id="rId144"/>
-    <hyperlink ref="E148" r:id="rId145"/>
-    <hyperlink ref="E149" r:id="rId146"/>
-    <hyperlink ref="E150" r:id="rId147"/>
-    <hyperlink ref="E151" r:id="rId148"/>
-    <hyperlink ref="E152" r:id="rId149"/>
-    <hyperlink ref="E153" r:id="rId150"/>
-    <hyperlink ref="E154" r:id="rId151"/>
-    <hyperlink ref="E155" r:id="rId152"/>
-    <hyperlink ref="E156" r:id="rId153"/>
-    <hyperlink ref="E157" r:id="rId154"/>
-    <hyperlink ref="E158" r:id="rId155"/>
-    <hyperlink ref="E159" r:id="rId156"/>
-    <hyperlink ref="E160" r:id="rId157"/>
-    <hyperlink ref="E161" r:id="rId158"/>
-    <hyperlink ref="E162" r:id="rId159"/>
-    <hyperlink ref="E163" r:id="rId160"/>
-    <hyperlink ref="E164" r:id="rId161"/>
-    <hyperlink ref="E165" r:id="rId162"/>
-    <hyperlink ref="E166" r:id="rId163"/>
-    <hyperlink ref="E167" r:id="rId164"/>
-    <hyperlink ref="E168" r:id="rId165"/>
-    <hyperlink ref="E169" r:id="rId166"/>
-    <hyperlink ref="E170" r:id="rId167"/>
-    <hyperlink ref="E172" r:id="rId168"/>
-    <hyperlink ref="E173" r:id="rId169"/>
-    <hyperlink ref="E174" r:id="rId170"/>
-    <hyperlink ref="E175" r:id="rId171"/>
-    <hyperlink ref="E176" r:id="rId172"/>
-    <hyperlink ref="E177" r:id="rId173"/>
-    <hyperlink ref="E178" r:id="rId174"/>
-    <hyperlink ref="E179" r:id="rId175"/>
-    <hyperlink ref="E180" r:id="rId176"/>
-    <hyperlink ref="E181" r:id="rId177"/>
-    <hyperlink ref="E182" r:id="rId178"/>
-    <hyperlink ref="E184" r:id="rId179"/>
-    <hyperlink ref="E185" r:id="rId180"/>
-    <hyperlink ref="E186" r:id="rId181"/>
-    <hyperlink ref="E187" r:id="rId182"/>
-    <hyperlink ref="E188" r:id="rId183"/>
-    <hyperlink ref="E189" r:id="rId184"/>
-    <hyperlink ref="E190" r:id="rId185"/>
-    <hyperlink ref="E191" r:id="rId186"/>
-    <hyperlink ref="E192" r:id="rId187"/>
-    <hyperlink ref="E193" r:id="rId188"/>
-    <hyperlink ref="E194" r:id="rId189"/>
-    <hyperlink ref="E195" r:id="rId190"/>
-    <hyperlink ref="E196" r:id="rId191"/>
-    <hyperlink ref="E198" r:id="rId192"/>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="C4" r:id="rId3"/>
+    <hyperlink ref="C5" r:id="rId4"/>
+    <hyperlink ref="C6" r:id="rId5"/>
+    <hyperlink ref="C7" r:id="rId6"/>
+    <hyperlink ref="C8" r:id="rId7"/>
+    <hyperlink ref="C9" r:id="rId8"/>
+    <hyperlink ref="C10" r:id="rId9"/>
+    <hyperlink ref="C11" r:id="rId10"/>
+    <hyperlink ref="C12" r:id="rId11"/>
+    <hyperlink ref="C13" r:id="rId12"/>
+    <hyperlink ref="C14" r:id="rId13"/>
+    <hyperlink ref="C15" r:id="rId14"/>
+    <hyperlink ref="C16" r:id="rId15"/>
+    <hyperlink ref="C17" r:id="rId16"/>
+    <hyperlink ref="C18" r:id="rId17"/>
+    <hyperlink ref="C19" r:id="rId18"/>
+    <hyperlink ref="C21" r:id="rId19"/>
+    <hyperlink ref="C22" r:id="rId20"/>
+    <hyperlink ref="C23" r:id="rId21"/>
+    <hyperlink ref="C24" r:id="rId22"/>
+    <hyperlink ref="C25" r:id="rId23"/>
+    <hyperlink ref="C26" r:id="rId24"/>
+    <hyperlink ref="C27" r:id="rId25"/>
+    <hyperlink ref="C28" r:id="rId26"/>
+    <hyperlink ref="C29" r:id="rId27"/>
+    <hyperlink ref="C30" r:id="rId28"/>
+    <hyperlink ref="C31" r:id="rId29"/>
+    <hyperlink ref="C32" r:id="rId30"/>
+    <hyperlink ref="C33" r:id="rId31"/>
+    <hyperlink ref="C34" r:id="rId32"/>
+    <hyperlink ref="C35" r:id="rId33"/>
+    <hyperlink ref="C36" r:id="rId34"/>
+    <hyperlink ref="C37" r:id="rId35"/>
+    <hyperlink ref="C38" r:id="rId36"/>
+    <hyperlink ref="C39" r:id="rId37"/>
+    <hyperlink ref="C40" r:id="rId38"/>
+    <hyperlink ref="C41" r:id="rId39"/>
+    <hyperlink ref="C42" r:id="rId40"/>
+    <hyperlink ref="C43" r:id="rId41"/>
+    <hyperlink ref="C44" r:id="rId42"/>
+    <hyperlink ref="C45" r:id="rId43"/>
+    <hyperlink ref="C46" r:id="rId44"/>
+    <hyperlink ref="C47" r:id="rId45"/>
+    <hyperlink ref="C48" r:id="rId46"/>
+    <hyperlink ref="C49" r:id="rId47"/>
+    <hyperlink ref="C50" r:id="rId48"/>
+    <hyperlink ref="C51" r:id="rId49"/>
+    <hyperlink ref="C52" r:id="rId50"/>
+    <hyperlink ref="C53" r:id="rId51"/>
+    <hyperlink ref="C54" r:id="rId52"/>
+    <hyperlink ref="C55" r:id="rId53"/>
+    <hyperlink ref="C56" r:id="rId54"/>
+    <hyperlink ref="C57" r:id="rId55"/>
+    <hyperlink ref="C58" r:id="rId56"/>
+    <hyperlink ref="C59" r:id="rId57"/>
+    <hyperlink ref="C60" r:id="rId58"/>
+    <hyperlink ref="C61" r:id="rId59"/>
+    <hyperlink ref="C62" r:id="rId60"/>
+    <hyperlink ref="C63" r:id="rId61"/>
+    <hyperlink ref="C64" r:id="rId62"/>
+    <hyperlink ref="C65" r:id="rId63"/>
+    <hyperlink ref="C66" r:id="rId64"/>
+    <hyperlink ref="C67" r:id="rId65"/>
+    <hyperlink ref="C68" r:id="rId66"/>
+    <hyperlink ref="C69" r:id="rId67"/>
+    <hyperlink ref="C70" r:id="rId68"/>
+    <hyperlink ref="C71" r:id="rId69"/>
+    <hyperlink ref="C72" r:id="rId70"/>
+    <hyperlink ref="C73" r:id="rId71"/>
+    <hyperlink ref="C74" r:id="rId72"/>
+    <hyperlink ref="C75" r:id="rId73"/>
+    <hyperlink ref="C76" r:id="rId74"/>
+    <hyperlink ref="C77" r:id="rId75"/>
+    <hyperlink ref="C78" r:id="rId76"/>
+    <hyperlink ref="C79" r:id="rId77"/>
+    <hyperlink ref="C80" r:id="rId78"/>
+    <hyperlink ref="C81" r:id="rId79"/>
+    <hyperlink ref="C82" r:id="rId80"/>
+    <hyperlink ref="C83" r:id="rId81"/>
+    <hyperlink ref="C84" r:id="rId82"/>
+    <hyperlink ref="C85" r:id="rId83"/>
+    <hyperlink ref="C86" r:id="rId84"/>
+    <hyperlink ref="C87" r:id="rId85"/>
+    <hyperlink ref="C88" r:id="rId86"/>
+    <hyperlink ref="C89" r:id="rId87"/>
+    <hyperlink ref="C90" r:id="rId88"/>
+    <hyperlink ref="C91" r:id="rId89"/>
+    <hyperlink ref="C92" r:id="rId90"/>
+    <hyperlink ref="C93" r:id="rId91"/>
+    <hyperlink ref="C94" r:id="rId92"/>
+    <hyperlink ref="C95" r:id="rId93"/>
+    <hyperlink ref="C96" r:id="rId94"/>
+    <hyperlink ref="C97" r:id="rId95"/>
+    <hyperlink ref="C98" r:id="rId96"/>
+    <hyperlink ref="C99" r:id="rId97"/>
+    <hyperlink ref="C100" r:id="rId98"/>
+    <hyperlink ref="C101" r:id="rId99"/>
+    <hyperlink ref="C102" r:id="rId100"/>
+    <hyperlink ref="C103" r:id="rId101"/>
+    <hyperlink ref="C104" r:id="rId102"/>
+    <hyperlink ref="C105" r:id="rId103"/>
+    <hyperlink ref="C106" r:id="rId104"/>
+    <hyperlink ref="C107" r:id="rId105"/>
+    <hyperlink ref="C108" r:id="rId106"/>
+    <hyperlink ref="C109" r:id="rId107"/>
+    <hyperlink ref="C110" r:id="rId108"/>
+    <hyperlink ref="C111" r:id="rId109"/>
+    <hyperlink ref="C112" r:id="rId110"/>
+    <hyperlink ref="C113" r:id="rId111"/>
+    <hyperlink ref="C114" r:id="rId112"/>
+    <hyperlink ref="C115" r:id="rId113"/>
+    <hyperlink ref="C116" r:id="rId114"/>
+    <hyperlink ref="C117" r:id="rId115"/>
+    <hyperlink ref="C118" r:id="rId116"/>
+    <hyperlink ref="C119" r:id="rId117"/>
+    <hyperlink ref="C120" r:id="rId118"/>
+    <hyperlink ref="C121" r:id="rId119"/>
+    <hyperlink ref="C122" r:id="rId120"/>
+    <hyperlink ref="C123" r:id="rId121"/>
+    <hyperlink ref="C124" r:id="rId122"/>
+    <hyperlink ref="C125" r:id="rId123"/>
+    <hyperlink ref="C126" r:id="rId124"/>
+    <hyperlink ref="C128" r:id="rId125"/>
+    <hyperlink ref="C129" r:id="rId126"/>
+    <hyperlink ref="C130" r:id="rId127"/>
+    <hyperlink ref="C131" r:id="rId128"/>
+    <hyperlink ref="C132" r:id="rId129"/>
+    <hyperlink ref="C133" r:id="rId130"/>
+    <hyperlink ref="C134" r:id="rId131"/>
+    <hyperlink ref="C135" r:id="rId132"/>
+    <hyperlink ref="C136" r:id="rId133"/>
+    <hyperlink ref="C137" r:id="rId134"/>
+    <hyperlink ref="C138" r:id="rId135"/>
+    <hyperlink ref="C139" r:id="rId136"/>
+    <hyperlink ref="C140" r:id="rId137"/>
+    <hyperlink ref="C141" r:id="rId138"/>
+    <hyperlink ref="C142" r:id="rId139"/>
+    <hyperlink ref="C143" r:id="rId140"/>
+    <hyperlink ref="C144" r:id="rId141"/>
+    <hyperlink ref="C145" r:id="rId142"/>
+    <hyperlink ref="C146" r:id="rId143"/>
+    <hyperlink ref="C147" r:id="rId144"/>
+    <hyperlink ref="C148" r:id="rId145"/>
+    <hyperlink ref="C149" r:id="rId146"/>
+    <hyperlink ref="C150" r:id="rId147"/>
+    <hyperlink ref="C151" r:id="rId148"/>
+    <hyperlink ref="C152" r:id="rId149"/>
+    <hyperlink ref="C153" r:id="rId150"/>
+    <hyperlink ref="C154" r:id="rId151"/>
+    <hyperlink ref="C155" r:id="rId152"/>
+    <hyperlink ref="C156" r:id="rId153"/>
+    <hyperlink ref="C157" r:id="rId154"/>
+    <hyperlink ref="C158" r:id="rId155"/>
+    <hyperlink ref="C159" r:id="rId156"/>
+    <hyperlink ref="C160" r:id="rId157"/>
+    <hyperlink ref="C161" r:id="rId158"/>
+    <hyperlink ref="C162" r:id="rId159"/>
+    <hyperlink ref="C163" r:id="rId160"/>
+    <hyperlink ref="C164" r:id="rId161"/>
+    <hyperlink ref="C165" r:id="rId162"/>
+    <hyperlink ref="C166" r:id="rId163"/>
+    <hyperlink ref="C167" r:id="rId164"/>
+    <hyperlink ref="C168" r:id="rId165"/>
+    <hyperlink ref="C169" r:id="rId166"/>
+    <hyperlink ref="C170" r:id="rId167"/>
+    <hyperlink ref="C172" r:id="rId168"/>
+    <hyperlink ref="C173" r:id="rId169"/>
+    <hyperlink ref="C174" r:id="rId170"/>
+    <hyperlink ref="C175" r:id="rId171"/>
+    <hyperlink ref="C176" r:id="rId172"/>
+    <hyperlink ref="C177" r:id="rId173"/>
+    <hyperlink ref="C178" r:id="rId174"/>
+    <hyperlink ref="C179" r:id="rId175"/>
+    <hyperlink ref="C180" r:id="rId176"/>
+    <hyperlink ref="C181" r:id="rId177"/>
+    <hyperlink ref="C182" r:id="rId178"/>
+    <hyperlink ref="C184" r:id="rId179"/>
+    <hyperlink ref="C185" r:id="rId180"/>
+    <hyperlink ref="C186" r:id="rId181"/>
+    <hyperlink ref="C187" r:id="rId182"/>
+    <hyperlink ref="C188" r:id="rId183"/>
+    <hyperlink ref="C189" r:id="rId184"/>
+    <hyperlink ref="C190" r:id="rId185"/>
+    <hyperlink ref="C191" r:id="rId186"/>
+    <hyperlink ref="C192" r:id="rId187"/>
+    <hyperlink ref="C193" r:id="rId188"/>
+    <hyperlink ref="C194" r:id="rId189"/>
+    <hyperlink ref="C195" r:id="rId190"/>
+    <hyperlink ref="C196" r:id="rId191"/>
+    <hyperlink ref="C198" r:id="rId192"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/clv3/xlsx/fr/OrganisationRegistrationAgency.xlsx
+++ b/api/clv3/xlsx/fr/OrganisationRegistrationAgency.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2169" uniqueCount="1336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2186" uniqueCount="1344">
   <si>
     <t>code</t>
   </si>
@@ -538,7 +538,7 @@
     <t>BR</t>
   </si>
   <si>
-    <t>http://cnpj.info/</t>
+    <t>https://www.gov.br/pt-br/servicos/consultar-cadastro-nacional-de-pessoas-juridicas</t>
   </si>
   <si>
     <t>BR-COA</t>
@@ -970,7 +970,7 @@
     <t>CZ-DIC</t>
   </si>
   <si>
-    <t>http://www.kurzy.cz/dic/</t>
+    <t>https://mfcr.cz/en/regulation-and-taxes/taxes</t>
   </si>
   <si>
     <t>CZ-ICO</t>
@@ -991,7 +991,7 @@
     <t>DE-CR</t>
   </si>
   <si>
-    <t>https://www.handelsregister.de/rp_web/welcome.do</t>
+    <t>https://www.handelsregister.de/rp_web/welcome.xhtml</t>
   </si>
   <si>
     <t>DJ-COA</t>
@@ -1162,7 +1162,7 @@
     <t>ET-CSA</t>
   </si>
   <si>
-    <t>http://www.chsa.gov.et/</t>
+    <t>https://acso.gov.et/</t>
   </si>
   <si>
     <t>ET-MFA</t>
@@ -2755,7 +2755,7 @@
     <t>NP-CRO</t>
   </si>
   <si>
-    <t>http://www.cro.gov.np/</t>
+    <t>https://www.ocr.gov.np/</t>
   </si>
   <si>
     <t>NP-IRD</t>
@@ -2860,6 +2860,12 @@
     <t>https://gov-id-finder.codeforiati.org/countries/PG/</t>
   </si>
   <si>
+    <t>PG-IPA</t>
+  </si>
+  <si>
+    <t>http://www.ipa.gov.pg/</t>
+  </si>
+  <si>
     <t>PH-COA</t>
   </si>
   <si>
@@ -3121,7 +3127,7 @@
     <t>RW-RRA</t>
   </si>
   <si>
-    <t>https://www.rra.gov.rw/index.php?id=45&amp;L=1%27A%3D0</t>
+    <t>https://www.rra.gov.rw/en/home</t>
   </si>
   <si>
     <t>SA-COA</t>
@@ -3133,12 +3139,18 @@
     <t>https://gov-id-finder.codeforiati.org/countries/SA/</t>
   </si>
   <si>
+    <t>SB-BR</t>
+  </si>
+  <si>
+    <t>SB</t>
+  </si>
+  <si>
+    <t>https://www.solomonbusinessregistry.gov.sb/</t>
+  </si>
+  <si>
     <t>SB-COA</t>
   </si>
   <si>
-    <t>SB</t>
-  </si>
-  <si>
     <t>https://gov-id-finder.codeforiati.org/countries/SB/</t>
   </si>
   <si>
@@ -3373,7 +3385,7 @@
     <t>SV-NIT</t>
   </si>
   <si>
-    <t>https://www.transparencia.gob.sv/institutions/dgii/services/7180</t>
+    <t>https://www.mh.gob.sv/</t>
   </si>
   <si>
     <t>SX-COA</t>
@@ -3547,6 +3559,12 @@
     <t>https://www.dernekler.gov.tr/</t>
   </si>
   <si>
+    <t>TR-VKN</t>
+  </si>
+  <si>
+    <t>https://www.gib.gov.tr/</t>
+  </si>
+  <si>
     <t>TT-COA</t>
   </si>
   <si>
@@ -3646,7 +3664,7 @@
     <t>UG-RSB</t>
   </si>
   <si>
-    <t>http://www.ursb.go.ug/</t>
+    <t>https://ursb.go.ug/</t>
   </si>
   <si>
     <t>UM-COA</t>
@@ -3775,6 +3793,12 @@
     <t>https://www.most.gov.vn/en/Pages/home.aspx</t>
   </si>
   <si>
+    <t>VN-TIN</t>
+  </si>
+  <si>
+    <t>https://vbpl.vn/TW/Pages/vbpqen-toanvan.aspx?ItemID=5946</t>
+  </si>
+  <si>
     <t>VU-COA</t>
   </si>
   <si>
@@ -3883,7 +3907,7 @@
     <t>XM-DAC</t>
   </si>
   <si>
-    <t>http://www.oecd.org/dac/stats/dacandcrscodelists.htm</t>
+    <t>https://development-finance-codelists.oecd.org/CodesList.aspx</t>
   </si>
   <si>
     <t>XM-OCHA</t>
@@ -3949,7 +3973,7 @@
     <t>ZA</t>
   </si>
   <si>
-    <t>http://www.cipro.gov.za/</t>
+    <t>https://www.cipc.co.za/</t>
   </si>
   <si>
     <t>ZA-CIT</t>
@@ -4366,7 +4390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E545"/>
+  <dimension ref="A1:E549"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5247,7 +5271,7 @@
         <v>8</v>
       </c>
       <c r="E52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -5907,7 +5931,7 @@
         <v>8</v>
       </c>
       <c r="E91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -7233,7 +7257,7 @@
         <v>8</v>
       </c>
       <c r="E169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -10732,7 +10756,7 @@
         <v>8</v>
       </c>
       <c r="E375" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -10961,10 +10985,10 @@
         <v>948</v>
       </c>
       <c r="B389" t="s">
+        <v>946</v>
+      </c>
+      <c r="C389" s="1" t="s">
         <v>949</v>
-      </c>
-      <c r="C389" s="1" t="s">
-        <v>950</v>
       </c>
       <c r="D389" t="s">
         <v>8</v>
@@ -10975,10 +10999,10 @@
     </row>
     <row r="390" spans="1:5">
       <c r="A390" t="s">
+        <v>950</v>
+      </c>
+      <c r="B390" t="s">
         <v>951</v>
-      </c>
-      <c r="B390" t="s">
-        <v>949</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>952</v>
@@ -10995,24 +11019,24 @@
         <v>953</v>
       </c>
       <c r="B391" t="s">
+        <v>951</v>
+      </c>
+      <c r="C391" s="1" t="s">
         <v>954</v>
       </c>
-      <c r="C391" s="1" t="s">
-        <v>955</v>
-      </c>
       <c r="D391" t="s">
         <v>8</v>
       </c>
       <c r="E391" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="392" spans="1:5">
       <c r="A392" t="s">
+        <v>955</v>
+      </c>
+      <c r="B392" t="s">
         <v>956</v>
-      </c>
-      <c r="B392" t="s">
-        <v>954</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>957</v>
@@ -11021,7 +11045,7 @@
         <v>8</v>
       </c>
       <c r="E392" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -11029,16 +11053,16 @@
         <v>958</v>
       </c>
       <c r="B393" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>959</v>
       </c>
       <c r="D393" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E393" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="394" spans="1:5">
@@ -11046,16 +11070,16 @@
         <v>960</v>
       </c>
       <c r="B394" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>961</v>
       </c>
       <c r="D394" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E394" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -11063,7 +11087,7 @@
         <v>962</v>
       </c>
       <c r="B395" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>963</v>
@@ -11072,7 +11096,7 @@
         <v>8</v>
       </c>
       <c r="E395" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="396" spans="1:5">
@@ -11080,10 +11104,10 @@
         <v>964</v>
       </c>
       <c r="B396" t="s">
+        <v>956</v>
+      </c>
+      <c r="C396" s="1" t="s">
         <v>965</v>
-      </c>
-      <c r="C396" s="1" t="s">
-        <v>966</v>
       </c>
       <c r="D396" t="s">
         <v>8</v>
@@ -11094,10 +11118,10 @@
     </row>
     <row r="397" spans="1:5">
       <c r="A397" t="s">
+        <v>966</v>
+      </c>
+      <c r="B397" t="s">
         <v>967</v>
-      </c>
-      <c r="B397" t="s">
-        <v>965</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>968</v>
@@ -11106,7 +11130,7 @@
         <v>8</v>
       </c>
       <c r="E397" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -11114,7 +11138,7 @@
         <v>969</v>
       </c>
       <c r="B398" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>970</v>
@@ -11131,7 +11155,7 @@
         <v>971</v>
       </c>
       <c r="B399" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>972</v>
@@ -11148,27 +11172,27 @@
         <v>973</v>
       </c>
       <c r="B400" t="s">
+        <v>967</v>
+      </c>
+      <c r="C400" s="1" t="s">
         <v>974</v>
       </c>
-      <c r="C400" s="1" t="s">
-        <v>975</v>
-      </c>
       <c r="D400" t="s">
         <v>8</v>
       </c>
       <c r="E400" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="401" spans="1:5">
       <c r="A401" t="s">
+        <v>975</v>
+      </c>
+      <c r="B401" t="s">
         <v>976</v>
       </c>
-      <c r="B401" t="s">
+      <c r="C401" s="1" t="s">
         <v>977</v>
-      </c>
-      <c r="C401" s="1" t="s">
-        <v>978</v>
       </c>
       <c r="D401" t="s">
         <v>8</v>
@@ -11179,13 +11203,13 @@
     </row>
     <row r="402" spans="1:5">
       <c r="A402" t="s">
+        <v>978</v>
+      </c>
+      <c r="B402" t="s">
         <v>979</v>
       </c>
-      <c r="B402" t="s">
+      <c r="C402" s="1" t="s">
         <v>980</v>
-      </c>
-      <c r="C402" s="1" t="s">
-        <v>981</v>
       </c>
       <c r="D402" t="s">
         <v>8</v>
@@ -11196,13 +11220,13 @@
     </row>
     <row r="403" spans="1:5">
       <c r="A403" t="s">
+        <v>981</v>
+      </c>
+      <c r="B403" t="s">
         <v>982</v>
       </c>
-      <c r="B403" t="s">
+      <c r="C403" s="1" t="s">
         <v>983</v>
-      </c>
-      <c r="C403" s="1" t="s">
-        <v>984</v>
       </c>
       <c r="D403" t="s">
         <v>8</v>
@@ -11213,10 +11237,10 @@
     </row>
     <row r="404" spans="1:5">
       <c r="A404" t="s">
+        <v>984</v>
+      </c>
+      <c r="B404" t="s">
         <v>985</v>
-      </c>
-      <c r="B404" t="s">
-        <v>983</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>986</v>
@@ -11233,7 +11257,7 @@
         <v>987</v>
       </c>
       <c r="B405" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>988</v>
@@ -11250,10 +11274,10 @@
         <v>989</v>
       </c>
       <c r="B406" t="s">
+        <v>985</v>
+      </c>
+      <c r="C406" s="1" t="s">
         <v>990</v>
-      </c>
-      <c r="C406" s="1" t="s">
-        <v>991</v>
       </c>
       <c r="D406" t="s">
         <v>8</v>
@@ -11264,10 +11288,10 @@
     </row>
     <row r="407" spans="1:5">
       <c r="A407" t="s">
+        <v>991</v>
+      </c>
+      <c r="B407" t="s">
         <v>992</v>
-      </c>
-      <c r="B407" t="s">
-        <v>990</v>
       </c>
       <c r="C407" s="1" t="s">
         <v>993</v>
@@ -11276,7 +11300,7 @@
         <v>8</v>
       </c>
       <c r="E407" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -11284,10 +11308,10 @@
         <v>994</v>
       </c>
       <c r="B408" t="s">
+        <v>992</v>
+      </c>
+      <c r="C408" s="1" t="s">
         <v>995</v>
-      </c>
-      <c r="C408" s="1" t="s">
-        <v>996</v>
       </c>
       <c r="D408" t="s">
         <v>8</v>
@@ -11298,27 +11322,27 @@
     </row>
     <row r="409" spans="1:5">
       <c r="A409" t="s">
+        <v>996</v>
+      </c>
+      <c r="B409" t="s">
         <v>997</v>
       </c>
-      <c r="B409" t="s">
+      <c r="C409" s="1" t="s">
         <v>998</v>
       </c>
-      <c r="C409" s="1" t="s">
-        <v>999</v>
-      </c>
       <c r="D409" t="s">
         <v>8</v>
       </c>
       <c r="E409" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410" spans="1:5">
       <c r="A410" t="s">
+        <v>999</v>
+      </c>
+      <c r="B410" t="s">
         <v>1000</v>
-      </c>
-      <c r="B410" t="s">
-        <v>998</v>
       </c>
       <c r="C410" s="1" t="s">
         <v>1001</v>
@@ -11327,7 +11351,7 @@
         <v>8</v>
       </c>
       <c r="E410" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="411" spans="1:5">
@@ -11335,7 +11359,7 @@
         <v>1002</v>
       </c>
       <c r="B411" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="C411" s="1" t="s">
         <v>1003</v>
@@ -11352,27 +11376,27 @@
         <v>1004</v>
       </c>
       <c r="B412" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C412" s="1" t="s">
         <v>1005</v>
       </c>
-      <c r="C412" s="1" t="s">
-        <v>1006</v>
-      </c>
       <c r="D412" t="s">
         <v>8</v>
       </c>
       <c r="E412" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="413" spans="1:5">
       <c r="A413" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B413" t="s">
         <v>1007</v>
       </c>
-      <c r="B413" t="s">
+      <c r="C413" s="1" t="s">
         <v>1008</v>
-      </c>
-      <c r="C413" s="1" t="s">
-        <v>1009</v>
       </c>
       <c r="D413" t="s">
         <v>8</v>
@@ -11383,13 +11407,13 @@
     </row>
     <row r="414" spans="1:5">
       <c r="A414" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B414" t="s">
         <v>1010</v>
       </c>
-      <c r="B414" t="s">
+      <c r="C414" s="1" t="s">
         <v>1011</v>
-      </c>
-      <c r="C414" s="1" t="s">
-        <v>1012</v>
       </c>
       <c r="D414" t="s">
         <v>8</v>
@@ -11400,10 +11424,10 @@
     </row>
     <row r="415" spans="1:5">
       <c r="A415" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B415" t="s">
         <v>1013</v>
-      </c>
-      <c r="B415" t="s">
-        <v>1011</v>
       </c>
       <c r="C415" s="1" t="s">
         <v>1014</v>
@@ -11412,7 +11436,7 @@
         <v>8</v>
       </c>
       <c r="E415" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="416" spans="1:5">
@@ -11420,24 +11444,24 @@
         <v>1015</v>
       </c>
       <c r="B416" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C416" s="1" t="s">
         <v>1016</v>
       </c>
-      <c r="C416" s="1" t="s">
-        <v>1017</v>
-      </c>
       <c r="D416" t="s">
         <v>8</v>
       </c>
       <c r="E416" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417" spans="1:5">
       <c r="A417" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B417" t="s">
         <v>1018</v>
-      </c>
-      <c r="B417" t="s">
-        <v>1016</v>
       </c>
       <c r="C417" s="1" t="s">
         <v>1019</v>
@@ -11454,7 +11478,7 @@
         <v>1020</v>
       </c>
       <c r="B418" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="C418" s="1" t="s">
         <v>1021</v>
@@ -11463,7 +11487,7 @@
         <v>8</v>
       </c>
       <c r="E418" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -11471,24 +11495,24 @@
         <v>1022</v>
       </c>
       <c r="B419" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C419" s="1" t="s">
         <v>1023</v>
       </c>
-      <c r="C419" s="1" t="s">
-        <v>1024</v>
-      </c>
       <c r="D419" t="s">
         <v>8</v>
       </c>
       <c r="E419" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="420" spans="1:5">
       <c r="A420" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B420" t="s">
         <v>1025</v>
-      </c>
-      <c r="B420" t="s">
-        <v>1023</v>
       </c>
       <c r="C420" s="1" t="s">
         <v>1026</v>
@@ -11497,7 +11521,7 @@
         <v>8</v>
       </c>
       <c r="E420" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="421" spans="1:5">
@@ -11505,7 +11529,7 @@
         <v>1027</v>
       </c>
       <c r="B421" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="C421" s="1" t="s">
         <v>1028</v>
@@ -11522,10 +11546,10 @@
         <v>1029</v>
       </c>
       <c r="B422" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C422" s="1" t="s">
         <v>1030</v>
-      </c>
-      <c r="C422" s="1" t="s">
-        <v>1031</v>
       </c>
       <c r="D422" t="s">
         <v>8</v>
@@ -11536,10 +11560,10 @@
     </row>
     <row r="423" spans="1:5">
       <c r="A423" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B423" t="s">
         <v>1032</v>
-      </c>
-      <c r="B423" t="s">
-        <v>1030</v>
       </c>
       <c r="C423" s="1" t="s">
         <v>1033</v>
@@ -11548,7 +11572,7 @@
         <v>8</v>
       </c>
       <c r="E423" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="424" spans="1:5">
@@ -11556,7 +11580,7 @@
         <v>1034</v>
       </c>
       <c r="B424" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="C424" s="1" t="s">
         <v>1035</v>
@@ -11573,10 +11597,10 @@
         <v>1036</v>
       </c>
       <c r="B425" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C425" s="1" t="s">
         <v>1037</v>
-      </c>
-      <c r="C425" s="1" t="s">
-        <v>1038</v>
       </c>
       <c r="D425" t="s">
         <v>8</v>
@@ -11587,67 +11611,67 @@
     </row>
     <row r="426" spans="1:5">
       <c r="A426" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B426" t="s">
         <v>1039</v>
       </c>
-      <c r="B426" t="s">
+      <c r="C426" s="1" t="s">
         <v>1040</v>
       </c>
-      <c r="C426" s="1" t="s">
-        <v>1041</v>
-      </c>
       <c r="D426" t="s">
         <v>8</v>
       </c>
       <c r="E426" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="427" spans="1:5">
       <c r="A427" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B427" t="s">
         <v>1042</v>
       </c>
-      <c r="B427" t="s">
+      <c r="C427" s="1" t="s">
         <v>1043</v>
       </c>
-      <c r="C427" s="1" t="s">
-        <v>1044</v>
-      </c>
       <c r="D427" t="s">
         <v>8</v>
       </c>
       <c r="E427" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="428" spans="1:5">
       <c r="A428" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B428" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C428" s="1" t="s">
         <v>1045</v>
       </c>
-      <c r="B428" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C428" s="1" t="s">
-        <v>1047</v>
-      </c>
       <c r="D428" t="s">
         <v>8</v>
       </c>
       <c r="E428" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="429" spans="1:5">
       <c r="A429" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B429" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C429" s="1" t="s">
         <v>1048</v>
       </c>
-      <c r="B429" t="s">
-        <v>1049</v>
-      </c>
-      <c r="C429" s="1" t="s">
-        <v>1050</v>
-      </c>
       <c r="D429" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E429" t="b">
         <v>0</v>
@@ -11655,13 +11679,13 @@
     </row>
     <row r="430" spans="1:5">
       <c r="A430" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B430" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C430" s="1" t="s">
         <v>1051</v>
-      </c>
-      <c r="B430" t="s">
-        <v>1049</v>
-      </c>
-      <c r="C430" s="1" t="s">
-        <v>1052</v>
       </c>
       <c r="D430" t="s">
         <v>8</v>
@@ -11672,10 +11696,10 @@
     </row>
     <row r="431" spans="1:5">
       <c r="A431" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B431" t="s">
         <v>1053</v>
-      </c>
-      <c r="B431" t="s">
-        <v>1049</v>
       </c>
       <c r="C431" s="1" t="s">
         <v>1054</v>
@@ -11692,7 +11716,7 @@
         <v>1055</v>
       </c>
       <c r="B432" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="C432" s="1" t="s">
         <v>1056</v>
@@ -11701,7 +11725,7 @@
         <v>8</v>
       </c>
       <c r="E432" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="433" spans="1:5">
@@ -11709,13 +11733,13 @@
         <v>1057</v>
       </c>
       <c r="B433" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C433" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="C433" s="1" t="s">
-        <v>1059</v>
-      </c>
       <c r="D433" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E433" t="b">
         <v>0</v>
@@ -11723,27 +11747,27 @@
     </row>
     <row r="434" spans="1:5">
       <c r="A434" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B434" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C434" s="1" t="s">
         <v>1060</v>
       </c>
-      <c r="B434" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C434" s="1" t="s">
-        <v>1061</v>
-      </c>
       <c r="D434" t="s">
         <v>8</v>
       </c>
       <c r="E434" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435" spans="1:5">
       <c r="A435" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B435" t="s">
         <v>1062</v>
-      </c>
-      <c r="B435" t="s">
-        <v>1058</v>
       </c>
       <c r="C435" s="1" t="s">
         <v>1063</v>
@@ -11752,7 +11776,7 @@
         <v>8</v>
       </c>
       <c r="E435" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="436" spans="1:5">
@@ -11760,10 +11784,10 @@
         <v>1064</v>
       </c>
       <c r="B436" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C436" s="1" t="s">
         <v>1065</v>
-      </c>
-      <c r="C436" s="1" t="s">
-        <v>1066</v>
       </c>
       <c r="D436" t="s">
         <v>8</v>
@@ -11774,44 +11798,44 @@
     </row>
     <row r="437" spans="1:5">
       <c r="A437" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B437" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C437" s="1" t="s">
         <v>1067</v>
       </c>
-      <c r="B437" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C437" s="1" t="s">
-        <v>1069</v>
-      </c>
       <c r="D437" t="s">
         <v>8</v>
       </c>
       <c r="E437" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="438" spans="1:5">
       <c r="A438" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B438" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C438" s="1" t="s">
         <v>1070</v>
       </c>
-      <c r="B438" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C438" s="1" t="s">
-        <v>1071</v>
-      </c>
       <c r="D438" t="s">
         <v>8</v>
       </c>
       <c r="E438" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="439" spans="1:5">
       <c r="A439" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B439" t="s">
         <v>1072</v>
-      </c>
-      <c r="B439" t="s">
-        <v>1068</v>
       </c>
       <c r="C439" s="1" t="s">
         <v>1073</v>
@@ -11820,7 +11844,7 @@
         <v>8</v>
       </c>
       <c r="E439" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -11828,58 +11852,58 @@
         <v>1074</v>
       </c>
       <c r="B440" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C440" s="1" t="s">
         <v>1075</v>
       </c>
-      <c r="C440" s="1" t="s">
-        <v>1076</v>
-      </c>
       <c r="D440" t="s">
         <v>8</v>
       </c>
       <c r="E440" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="441" spans="1:5">
       <c r="A441" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B441" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C441" s="1" t="s">
         <v>1077</v>
       </c>
-      <c r="B441" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C441" s="1" t="s">
-        <v>1079</v>
-      </c>
       <c r="D441" t="s">
         <v>8</v>
       </c>
       <c r="E441" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="442" spans="1:5">
       <c r="A442" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B442" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C442" s="1" t="s">
         <v>1080</v>
       </c>
-      <c r="B442" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C442" s="1" t="s">
-        <v>1081</v>
-      </c>
       <c r="D442" t="s">
         <v>8</v>
       </c>
       <c r="E442" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="443" spans="1:5">
       <c r="A443" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B443" t="s">
         <v>1082</v>
-      </c>
-      <c r="B443" t="s">
-        <v>1078</v>
       </c>
       <c r="C443" s="1" t="s">
         <v>1083</v>
@@ -11896,24 +11920,24 @@
         <v>1084</v>
       </c>
       <c r="B444" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="C444" s="1" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="D444" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E444" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="445" spans="1:5">
       <c r="A445" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B445" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="C445" s="1" t="s">
         <v>1087</v>
@@ -11922,7 +11946,7 @@
         <v>8</v>
       </c>
       <c r="E445" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="446" spans="1:5">
@@ -11930,13 +11954,13 @@
         <v>1088</v>
       </c>
       <c r="B446" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="C446" s="1" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="D446" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E446" t="b">
         <v>0</v>
@@ -11944,10 +11968,10 @@
     </row>
     <row r="447" spans="1:5">
       <c r="A447" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B447" t="s">
         <v>1090</v>
-      </c>
-      <c r="B447" t="s">
-        <v>1086</v>
       </c>
       <c r="C447" s="1" t="s">
         <v>1091</v>
@@ -11956,7 +11980,7 @@
         <v>8</v>
       </c>
       <c r="E447" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="448" spans="1:5">
@@ -11964,10 +11988,10 @@
         <v>1092</v>
       </c>
       <c r="B448" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C448" s="1" t="s">
         <v>1093</v>
-      </c>
-      <c r="C448" s="1" t="s">
-        <v>1094</v>
       </c>
       <c r="D448" t="s">
         <v>8</v>
@@ -11978,47 +12002,47 @@
     </row>
     <row r="449" spans="1:5">
       <c r="A449" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B449" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C449" s="1" t="s">
         <v>1095</v>
       </c>
-      <c r="B449" t="s">
-        <v>1096</v>
-      </c>
-      <c r="C449" s="1" t="s">
-        <v>1097</v>
-      </c>
       <c r="D449" t="s">
         <v>8</v>
       </c>
       <c r="E449" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="450" spans="1:5">
       <c r="A450" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B450" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C450" s="1" t="s">
         <v>1098</v>
       </c>
-      <c r="B450" t="s">
-        <v>1096</v>
-      </c>
-      <c r="C450" s="1" t="s">
-        <v>1099</v>
-      </c>
       <c r="D450" t="s">
         <v>8</v>
       </c>
       <c r="E450" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="451" spans="1:5">
       <c r="A451" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B451" t="s">
         <v>1100</v>
       </c>
-      <c r="B451" t="s">
+      <c r="C451" s="1" t="s">
         <v>1101</v>
-      </c>
-      <c r="C451" s="1" t="s">
-        <v>1102</v>
       </c>
       <c r="D451" t="s">
         <v>8</v>
@@ -12029,47 +12053,47 @@
     </row>
     <row r="452" spans="1:5">
       <c r="A452" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B452" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C452" s="1" t="s">
         <v>1103</v>
       </c>
-      <c r="B452" t="s">
-        <v>1101</v>
-      </c>
-      <c r="C452" s="1" t="s">
-        <v>1104</v>
-      </c>
       <c r="D452" t="s">
         <v>8</v>
       </c>
       <c r="E452" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453" spans="1:5">
       <c r="A453" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B453" t="s">
         <v>1105</v>
       </c>
-      <c r="B453" t="s">
+      <c r="C453" s="1" t="s">
         <v>1106</v>
       </c>
-      <c r="C453" s="1" t="s">
-        <v>1107</v>
-      </c>
       <c r="D453" t="s">
         <v>8</v>
       </c>
       <c r="E453" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454" spans="1:5">
       <c r="A454" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B454" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C454" s="1" t="s">
         <v>1108</v>
-      </c>
-      <c r="B454" t="s">
-        <v>1109</v>
-      </c>
-      <c r="C454" s="1" t="s">
-        <v>1110</v>
       </c>
       <c r="D454" t="s">
         <v>8</v>
@@ -12080,10 +12104,13 @@
     </row>
     <row r="455" spans="1:5">
       <c r="A455" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B455" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C455" s="1" t="s">
         <v>1111</v>
-      </c>
-      <c r="B455" t="s">
-        <v>1109</v>
       </c>
       <c r="D455" t="s">
         <v>8</v>
@@ -12114,10 +12141,7 @@
         <v>1115</v>
       </c>
       <c r="B457" t="s">
-        <v>1116</v>
-      </c>
-      <c r="C457" s="1" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="D457" t="s">
         <v>8</v>
@@ -12128,13 +12152,13 @@
     </row>
     <row r="458" spans="1:5">
       <c r="A458" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B458" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C458" s="1" t="s">
         <v>1118</v>
-      </c>
-      <c r="B458" t="s">
-        <v>1116</v>
-      </c>
-      <c r="C458" s="1" t="s">
-        <v>1119</v>
       </c>
       <c r="D458" t="s">
         <v>8</v>
@@ -12145,13 +12169,13 @@
     </row>
     <row r="459" spans="1:5">
       <c r="A459" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B459" t="s">
         <v>1120</v>
       </c>
-      <c r="B459" t="s">
+      <c r="C459" s="1" t="s">
         <v>1121</v>
-      </c>
-      <c r="C459" s="1" t="s">
-        <v>1122</v>
       </c>
       <c r="D459" t="s">
         <v>8</v>
@@ -12162,13 +12186,13 @@
     </row>
     <row r="460" spans="1:5">
       <c r="A460" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B460" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C460" s="1" t="s">
         <v>1123</v>
-      </c>
-      <c r="B460" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C460" s="1" t="s">
-        <v>1125</v>
       </c>
       <c r="D460" t="s">
         <v>8</v>
@@ -12179,64 +12203,64 @@
     </row>
     <row r="461" spans="1:5">
       <c r="A461" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B461" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C461" s="1" t="s">
         <v>1126</v>
       </c>
-      <c r="B461" t="s">
-        <v>1127</v>
-      </c>
-      <c r="C461" s="1" t="s">
-        <v>1128</v>
-      </c>
       <c r="D461" t="s">
         <v>8</v>
       </c>
       <c r="E461" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="462" spans="1:5">
       <c r="A462" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B462" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C462" s="1" t="s">
         <v>1129</v>
       </c>
-      <c r="B462" t="s">
-        <v>1127</v>
-      </c>
-      <c r="C462" s="1" t="s">
-        <v>1130</v>
-      </c>
       <c r="D462" t="s">
         <v>8</v>
       </c>
       <c r="E462" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="463" spans="1:5">
       <c r="A463" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B463" t="s">
         <v>1131</v>
       </c>
-      <c r="B463" t="s">
+      <c r="C463" s="1" t="s">
         <v>1132</v>
       </c>
-      <c r="C463" s="1" t="s">
-        <v>1133</v>
-      </c>
       <c r="D463" t="s">
         <v>8</v>
       </c>
       <c r="E463" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="464" spans="1:5">
       <c r="A464" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B464" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C464" s="1" t="s">
         <v>1134</v>
-      </c>
-      <c r="B464" t="s">
-        <v>1135</v>
-      </c>
-      <c r="C464" s="1" t="s">
-        <v>1136</v>
       </c>
       <c r="D464" t="s">
         <v>8</v>
@@ -12247,13 +12271,13 @@
     </row>
     <row r="465" spans="1:5">
       <c r="A465" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B465" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C465" s="1" t="s">
         <v>1137</v>
-      </c>
-      <c r="B465" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C465" s="1" t="s">
-        <v>1139</v>
       </c>
       <c r="D465" t="s">
         <v>8</v>
@@ -12264,13 +12288,13 @@
     </row>
     <row r="466" spans="1:5">
       <c r="A466" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B466" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C466" s="1" t="s">
         <v>1140</v>
-      </c>
-      <c r="B466" t="s">
-        <v>1141</v>
-      </c>
-      <c r="C466" s="1" t="s">
-        <v>1142</v>
       </c>
       <c r="D466" t="s">
         <v>8</v>
@@ -12281,13 +12305,13 @@
     </row>
     <row r="467" spans="1:5">
       <c r="A467" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B467" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C467" s="1" t="s">
         <v>1143</v>
-      </c>
-      <c r="B467" t="s">
-        <v>1144</v>
-      </c>
-      <c r="C467" s="1" t="s">
-        <v>1145</v>
       </c>
       <c r="D467" t="s">
         <v>8</v>
@@ -12298,27 +12322,27 @@
     </row>
     <row r="468" spans="1:5">
       <c r="A468" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B468" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C468" s="1" t="s">
         <v>1146</v>
       </c>
-      <c r="B468" t="s">
-        <v>1144</v>
-      </c>
-      <c r="C468" s="1" t="s">
-        <v>1147</v>
-      </c>
       <c r="D468" t="s">
         <v>8</v>
       </c>
       <c r="E468" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="469" spans="1:5">
       <c r="A469" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B469" t="s">
         <v>1148</v>
-      </c>
-      <c r="B469" t="s">
-        <v>1144</v>
       </c>
       <c r="C469" s="1" t="s">
         <v>1149</v>
@@ -12335,10 +12359,10 @@
         <v>1150</v>
       </c>
       <c r="B470" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C470" s="1" t="s">
         <v>1151</v>
-      </c>
-      <c r="C470" s="1" t="s">
-        <v>1152</v>
       </c>
       <c r="D470" t="s">
         <v>8</v>
@@ -12349,13 +12373,13 @@
     </row>
     <row r="471" spans="1:5">
       <c r="A471" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B471" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C471" s="1" t="s">
         <v>1153</v>
-      </c>
-      <c r="B471" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C471" s="1" t="s">
-        <v>1155</v>
       </c>
       <c r="D471" t="s">
         <v>8</v>
@@ -12366,30 +12390,30 @@
     </row>
     <row r="472" spans="1:5">
       <c r="A472" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B472" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C472" s="1" t="s">
         <v>1156</v>
       </c>
-      <c r="B472" t="s">
-        <v>1157</v>
-      </c>
-      <c r="C472" s="1" t="s">
-        <v>1158</v>
-      </c>
       <c r="D472" t="s">
         <v>8</v>
       </c>
       <c r="E472" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="473" spans="1:5">
       <c r="A473" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B473" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C473" s="1" t="s">
         <v>1159</v>
-      </c>
-      <c r="B473" t="s">
-        <v>1160</v>
-      </c>
-      <c r="C473" s="1" t="s">
-        <v>1161</v>
       </c>
       <c r="D473" t="s">
         <v>8</v>
@@ -12400,30 +12424,30 @@
     </row>
     <row r="474" spans="1:5">
       <c r="A474" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B474" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C474" s="1" t="s">
         <v>1162</v>
       </c>
-      <c r="B474" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C474" s="1" t="s">
-        <v>1164</v>
-      </c>
       <c r="D474" t="s">
         <v>8</v>
       </c>
       <c r="E474" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="475" spans="1:5">
       <c r="A475" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B475" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C475" s="1" t="s">
         <v>1165</v>
-      </c>
-      <c r="B475" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C475" s="1" t="s">
-        <v>1166</v>
       </c>
       <c r="D475" t="s">
         <v>8</v>
@@ -12434,13 +12458,13 @@
     </row>
     <row r="476" spans="1:5">
       <c r="A476" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B476" t="s">
         <v>1167</v>
       </c>
-      <c r="B476" t="s">
+      <c r="C476" s="1" t="s">
         <v>1168</v>
-      </c>
-      <c r="C476" s="1" t="s">
-        <v>1169</v>
       </c>
       <c r="D476" t="s">
         <v>8</v>
@@ -12451,13 +12475,13 @@
     </row>
     <row r="477" spans="1:5">
       <c r="A477" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B477" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C477" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="B477" t="s">
-        <v>1171</v>
-      </c>
-      <c r="C477" s="1" t="s">
-        <v>1172</v>
       </c>
       <c r="D477" t="s">
         <v>8</v>
@@ -12468,27 +12492,27 @@
     </row>
     <row r="478" spans="1:5">
       <c r="A478" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B478" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C478" s="1" t="s">
         <v>1173</v>
       </c>
-      <c r="B478" t="s">
-        <v>1171</v>
-      </c>
-      <c r="C478" s="1" t="s">
-        <v>1174</v>
-      </c>
       <c r="D478" t="s">
         <v>8</v>
       </c>
       <c r="E478" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="479" spans="1:5">
       <c r="A479" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B479" t="s">
         <v>1175</v>
-      </c>
-      <c r="B479" t="s">
-        <v>1171</v>
       </c>
       <c r="C479" s="1" t="s">
         <v>1176</v>
@@ -12505,27 +12529,27 @@
         <v>1177</v>
       </c>
       <c r="B480" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C480" s="1" t="s">
         <v>1178</v>
       </c>
-      <c r="C480" s="1" t="s">
-        <v>1179</v>
-      </c>
       <c r="D480" t="s">
         <v>8</v>
       </c>
       <c r="E480" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="481" spans="1:5">
       <c r="A481" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B481" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C481" s="1" t="s">
         <v>1180</v>
-      </c>
-      <c r="B481" t="s">
-        <v>1181</v>
-      </c>
-      <c r="C481" s="1" t="s">
-        <v>1182</v>
       </c>
       <c r="D481" t="s">
         <v>8</v>
@@ -12536,13 +12560,13 @@
     </row>
     <row r="482" spans="1:5">
       <c r="A482" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="B482" t="s">
-        <v>1184</v>
+        <v>1175</v>
       </c>
       <c r="C482" s="1" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="D482" t="s">
         <v>8</v>
@@ -12553,13 +12577,13 @@
     </row>
     <row r="483" spans="1:5">
       <c r="A483" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="B483" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="C483" s="1" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="D483" t="s">
         <v>8</v>
@@ -12570,30 +12594,30 @@
     </row>
     <row r="484" spans="1:5">
       <c r="A484" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="B484" t="s">
         <v>1187</v>
       </c>
       <c r="C484" s="1" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="D484" t="s">
         <v>8</v>
       </c>
       <c r="E484" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="485" spans="1:5">
       <c r="A485" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B485" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C485" s="1" t="s">
         <v>1191</v>
-      </c>
-      <c r="B485" t="s">
-        <v>1187</v>
-      </c>
-      <c r="C485" s="1" t="s">
-        <v>1192</v>
       </c>
       <c r="D485" t="s">
         <v>8</v>
@@ -12604,10 +12628,10 @@
     </row>
     <row r="486" spans="1:5">
       <c r="A486" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B486" t="s">
         <v>1193</v>
-      </c>
-      <c r="B486" t="s">
-        <v>1187</v>
       </c>
       <c r="C486" s="1" t="s">
         <v>1194</v>
@@ -12624,27 +12648,27 @@
         <v>1195</v>
       </c>
       <c r="B487" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C487" s="1" t="s">
         <v>1196</v>
       </c>
-      <c r="C487" s="1" t="s">
-        <v>1197</v>
-      </c>
       <c r="D487" t="s">
         <v>8</v>
       </c>
       <c r="E487" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="488" spans="1:5">
       <c r="A488" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B488" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C488" s="1" t="s">
         <v>1198</v>
-      </c>
-      <c r="B488" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C488" s="1" t="s">
-        <v>1199</v>
       </c>
       <c r="D488" t="s">
         <v>8</v>
@@ -12655,13 +12679,13 @@
     </row>
     <row r="489" spans="1:5">
       <c r="A489" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B489" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C489" s="1" t="s">
         <v>1200</v>
-      </c>
-      <c r="B489" t="s">
-        <v>1201</v>
-      </c>
-      <c r="C489" s="1" t="s">
-        <v>1202</v>
       </c>
       <c r="D489" t="s">
         <v>8</v>
@@ -12672,33 +12696,33 @@
     </row>
     <row r="490" spans="1:5">
       <c r="A490" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B490" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C490" s="1" t="s">
         <v>1203</v>
       </c>
-      <c r="B490" t="s">
-        <v>1201</v>
-      </c>
-      <c r="C490" s="1" t="s">
-        <v>1204</v>
-      </c>
       <c r="D490" t="s">
         <v>8</v>
       </c>
       <c r="E490" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="491" spans="1:5">
       <c r="A491" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B491" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C491" s="1" t="s">
         <v>1205</v>
       </c>
-      <c r="B491" t="s">
-        <v>1201</v>
-      </c>
-      <c r="C491" s="1" t="s">
-        <v>1206</v>
-      </c>
       <c r="D491" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E491" t="b">
         <v>0</v>
@@ -12706,10 +12730,10 @@
     </row>
     <row r="492" spans="1:5">
       <c r="A492" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B492" t="s">
         <v>1207</v>
-      </c>
-      <c r="B492" t="s">
-        <v>1201</v>
       </c>
       <c r="C492" s="1" t="s">
         <v>1208</v>
@@ -12718,7 +12742,7 @@
         <v>8</v>
       </c>
       <c r="E492" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="493" spans="1:5">
@@ -12726,7 +12750,7 @@
         <v>1209</v>
       </c>
       <c r="B493" t="s">
-        <v>1201</v>
+        <v>1207</v>
       </c>
       <c r="C493" s="1" t="s">
         <v>1210</v>
@@ -12735,7 +12759,7 @@
         <v>8</v>
       </c>
       <c r="E493" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="494" spans="1:5">
@@ -12743,13 +12767,13 @@
         <v>1211</v>
       </c>
       <c r="B494" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C494" s="1" t="s">
         <v>1212</v>
       </c>
-      <c r="C494" s="1" t="s">
-        <v>1213</v>
-      </c>
       <c r="D494" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E494" t="b">
         <v>0</v>
@@ -12757,47 +12781,47 @@
     </row>
     <row r="495" spans="1:5">
       <c r="A495" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B495" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C495" s="1" t="s">
         <v>1214</v>
       </c>
-      <c r="B495" t="s">
-        <v>1215</v>
-      </c>
-      <c r="C495" s="1" t="s">
-        <v>1216</v>
-      </c>
       <c r="D495" t="s">
         <v>8</v>
       </c>
       <c r="E495" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="496" spans="1:5">
       <c r="A496" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="B496" t="s">
-        <v>1215</v>
+        <v>1207</v>
       </c>
       <c r="C496" s="1" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="D496" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E496" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="497" spans="1:5">
       <c r="A497" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B497" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C497" s="1" t="s">
         <v>1219</v>
-      </c>
-      <c r="B497" t="s">
-        <v>1215</v>
-      </c>
-      <c r="C497" s="1" t="s">
-        <v>1220</v>
       </c>
       <c r="D497" t="s">
         <v>8</v>
@@ -12808,10 +12832,10 @@
     </row>
     <row r="498" spans="1:5">
       <c r="A498" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B498" t="s">
         <v>1221</v>
-      </c>
-      <c r="B498" t="s">
-        <v>1215</v>
       </c>
       <c r="C498" s="1" t="s">
         <v>1222</v>
@@ -12820,7 +12844,7 @@
         <v>8</v>
       </c>
       <c r="E498" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="499" spans="1:5">
@@ -12828,13 +12852,13 @@
         <v>1223</v>
       </c>
       <c r="B499" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
       <c r="C499" s="1" t="s">
         <v>1224</v>
       </c>
       <c r="D499" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E499" t="b">
         <v>0</v>
@@ -12845,10 +12869,10 @@
         <v>1225</v>
       </c>
       <c r="B500" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C500" s="1" t="s">
         <v>1226</v>
-      </c>
-      <c r="C500" s="1" t="s">
-        <v>1227</v>
       </c>
       <c r="D500" t="s">
         <v>8</v>
@@ -12859,30 +12883,30 @@
     </row>
     <row r="501" spans="1:5">
       <c r="A501" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B501" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C501" s="1" t="s">
         <v>1228</v>
       </c>
-      <c r="B501" t="s">
-        <v>1229</v>
-      </c>
-      <c r="C501" s="1" t="s">
-        <v>1230</v>
-      </c>
       <c r="D501" t="s">
         <v>8</v>
       </c>
       <c r="E501" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="502" spans="1:5">
       <c r="A502" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="B502" t="s">
-        <v>1229</v>
+        <v>1221</v>
       </c>
       <c r="C502" s="1" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="D502" t="s">
         <v>8</v>
@@ -12893,13 +12917,13 @@
     </row>
     <row r="503" spans="1:5">
       <c r="A503" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B503" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C503" s="1" t="s">
         <v>1233</v>
-      </c>
-      <c r="B503" t="s">
-        <v>1234</v>
-      </c>
-      <c r="C503" s="1" t="s">
-        <v>1235</v>
       </c>
       <c r="D503" t="s">
         <v>8</v>
@@ -12910,13 +12934,13 @@
     </row>
     <row r="504" spans="1:5">
       <c r="A504" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B504" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C504" s="1" t="s">
         <v>1236</v>
-      </c>
-      <c r="B504" t="s">
-        <v>1237</v>
-      </c>
-      <c r="C504" s="1" t="s">
-        <v>1238</v>
       </c>
       <c r="D504" t="s">
         <v>8</v>
@@ -12927,13 +12951,13 @@
     </row>
     <row r="505" spans="1:5">
       <c r="A505" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="B505" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
       <c r="C505" s="1" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="D505" t="s">
         <v>8</v>
@@ -12944,13 +12968,13 @@
     </row>
     <row r="506" spans="1:5">
       <c r="A506" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="B506" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="C506" s="1" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="D506" t="s">
         <v>8</v>
@@ -12961,13 +12985,13 @@
     </row>
     <row r="507" spans="1:5">
       <c r="A507" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="B507" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="C507" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="D507" t="s">
         <v>8</v>
@@ -12978,13 +13002,13 @@
     </row>
     <row r="508" spans="1:5">
       <c r="A508" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="B508" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="C508" s="1" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="D508" t="s">
         <v>8</v>
@@ -12995,13 +13019,13 @@
     </row>
     <row r="509" spans="1:5">
       <c r="A509" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="B509" t="s">
         <v>1249</v>
       </c>
       <c r="C509" s="1" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="D509" t="s">
         <v>8</v>
@@ -13012,13 +13036,13 @@
     </row>
     <row r="510" spans="1:5">
       <c r="A510" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C510" s="1" t="s">
         <v>1253</v>
-      </c>
-      <c r="B510" t="s">
-        <v>1254</v>
-      </c>
-      <c r="C510" s="1" t="s">
-        <v>1255</v>
       </c>
       <c r="D510" t="s">
         <v>8</v>
@@ -13029,13 +13053,13 @@
     </row>
     <row r="511" spans="1:5">
       <c r="A511" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B511" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C511" s="1" t="s">
         <v>1256</v>
-      </c>
-      <c r="B511" t="s">
-        <v>1257</v>
-      </c>
-      <c r="C511" s="1" t="s">
-        <v>1258</v>
       </c>
       <c r="D511" t="s">
         <v>8</v>
@@ -13046,13 +13070,13 @@
     </row>
     <row r="512" spans="1:5">
       <c r="A512" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="B512" t="s">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="C512" s="1" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="D512" t="s">
         <v>8</v>
@@ -13063,7 +13087,13 @@
     </row>
     <row r="513" spans="1:5">
       <c r="A513" t="s">
-        <v>1262</v>
+        <v>1259</v>
+      </c>
+      <c r="B513" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C513" s="1" t="s">
+        <v>1260</v>
       </c>
       <c r="D513" t="s">
         <v>8</v>
@@ -13074,41 +13104,44 @@
     </row>
     <row r="514" spans="1:5">
       <c r="A514" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B514" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C514" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="C514" s="1" t="s">
-        <v>1264</v>
-      </c>
       <c r="D514" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E514" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="515" spans="1:5">
       <c r="A515" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B515" t="s">
         <v>1265</v>
       </c>
-      <c r="B515" t="s">
+      <c r="C515" s="1" t="s">
         <v>1266</v>
       </c>
-      <c r="C515" s="1" t="s">
-        <v>1267</v>
-      </c>
       <c r="D515" t="s">
         <v>8</v>
       </c>
       <c r="E515" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="516" spans="1:5">
       <c r="A516" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B516" t="s">
         <v>1268</v>
-      </c>
-      <c r="B516" t="s">
-        <v>1266</v>
       </c>
       <c r="C516" s="1" t="s">
         <v>1269</v>
@@ -13124,9 +13157,6 @@
       <c r="A517" t="s">
         <v>1270</v>
       </c>
-      <c r="C517" s="1" t="s">
-        <v>1271</v>
-      </c>
       <c r="D517" t="s">
         <v>8</v>
       </c>
@@ -13136,24 +13166,24 @@
     </row>
     <row r="518" spans="1:5">
       <c r="A518" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C518" s="1" t="s">
         <v>1272</v>
       </c>
-      <c r="C518" s="1" t="s">
-        <v>1273</v>
-      </c>
       <c r="D518" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E518" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="519" spans="1:5">
       <c r="A519" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B519" t="s">
         <v>1274</v>
-      </c>
-      <c r="B519" t="s">
-        <v>1266</v>
       </c>
       <c r="C519" s="1" t="s">
         <v>1275</v>
@@ -13170,10 +13200,10 @@
         <v>1276</v>
       </c>
       <c r="B520" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C520" s="1" t="s">
         <v>1277</v>
-      </c>
-      <c r="C520" s="1" t="s">
-        <v>1278</v>
       </c>
       <c r="D520" t="s">
         <v>8</v>
@@ -13184,47 +13214,44 @@
     </row>
     <row r="521" spans="1:5">
       <c r="A521" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B521" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C521" s="1" t="s">
         <v>1279</v>
       </c>
-      <c r="B521" t="s">
-        <v>1266</v>
-      </c>
-      <c r="C521" s="1" t="s">
-        <v>1280</v>
-      </c>
       <c r="D521" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E521" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="522" spans="1:5">
       <c r="A522" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C522" s="1" t="s">
         <v>1281</v>
       </c>
-      <c r="B522" t="s">
-        <v>1266</v>
-      </c>
-      <c r="C522" s="1" t="s">
-        <v>1282</v>
-      </c>
       <c r="D522" t="s">
         <v>8</v>
       </c>
       <c r="E522" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="523" spans="1:5">
       <c r="A523" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B523" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C523" s="1" t="s">
         <v>1283</v>
-      </c>
-      <c r="B523" t="s">
-        <v>1266</v>
-      </c>
-      <c r="C523" s="1" t="s">
-        <v>1284</v>
       </c>
       <c r="D523" t="s">
         <v>8</v>
@@ -13235,13 +13262,13 @@
     </row>
     <row r="524" spans="1:5">
       <c r="A524" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B524" t="s">
         <v>1285</v>
       </c>
-      <c r="B524" t="s">
+      <c r="C524" s="1" t="s">
         <v>1286</v>
-      </c>
-      <c r="C524" s="1" t="s">
-        <v>1287</v>
       </c>
       <c r="D524" t="s">
         <v>8</v>
@@ -13252,24 +13279,30 @@
     </row>
     <row r="525" spans="1:5">
       <c r="A525" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B525" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C525" s="1" t="s">
         <v>1288</v>
       </c>
-      <c r="C525" s="1" t="s">
-        <v>1289</v>
-      </c>
       <c r="D525" t="s">
         <v>8</v>
       </c>
       <c r="E525" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="526" spans="1:5">
       <c r="A526" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B526" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C526" s="1" t="s">
         <v>1290</v>
-      </c>
-      <c r="C526" s="1" t="s">
-        <v>1291</v>
       </c>
       <c r="D526" t="s">
         <v>8</v>
@@ -13280,13 +13313,13 @@
     </row>
     <row r="527" spans="1:5">
       <c r="A527" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C527" s="1" t="s">
         <v>1292</v>
-      </c>
-      <c r="B527" t="s">
-        <v>1266</v>
-      </c>
-      <c r="C527" s="1" t="s">
-        <v>1293</v>
       </c>
       <c r="D527" t="s">
         <v>8</v>
@@ -13297,13 +13330,13 @@
     </row>
     <row r="528" spans="1:5">
       <c r="A528" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B528" t="s">
         <v>1294</v>
       </c>
-      <c r="B528" t="s">
+      <c r="C528" s="1" t="s">
         <v>1295</v>
-      </c>
-      <c r="C528" s="1" t="s">
-        <v>1296</v>
       </c>
       <c r="D528" t="s">
         <v>8</v>
@@ -13314,30 +13347,24 @@
     </row>
     <row r="529" spans="1:5">
       <c r="A529" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C529" s="1" t="s">
         <v>1297</v>
       </c>
-      <c r="B529" t="s">
-        <v>1298</v>
-      </c>
-      <c r="C529" s="1" t="s">
-        <v>1299</v>
-      </c>
       <c r="D529" t="s">
         <v>8</v>
       </c>
       <c r="E529" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="530" spans="1:5">
       <c r="A530" t="s">
-        <v>1300</v>
-      </c>
-      <c r="B530" t="s">
         <v>1298</v>
       </c>
       <c r="C530" s="1" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D530" t="s">
         <v>8</v>
@@ -13348,30 +13375,30 @@
     </row>
     <row r="531" spans="1:5">
       <c r="A531" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="B531" t="s">
-        <v>1298</v>
+        <v>1274</v>
       </c>
       <c r="C531" s="1" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="D531" t="s">
         <v>8</v>
       </c>
       <c r="E531" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="532" spans="1:5">
       <c r="A532" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B532" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C532" s="1" t="s">
         <v>1304</v>
-      </c>
-      <c r="B532" t="s">
-        <v>1298</v>
-      </c>
-      <c r="C532" s="1" t="s">
-        <v>1305</v>
       </c>
       <c r="D532" t="s">
         <v>8</v>
@@ -13382,13 +13409,13 @@
     </row>
     <row r="533" spans="1:5">
       <c r="A533" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B533" t="s">
         <v>1306</v>
       </c>
-      <c r="B533" t="s">
+      <c r="C533" s="1" t="s">
         <v>1307</v>
-      </c>
-      <c r="C533" s="1" t="s">
-        <v>1308</v>
       </c>
       <c r="D533" t="s">
         <v>8</v>
@@ -13399,30 +13426,30 @@
     </row>
     <row r="534" spans="1:5">
       <c r="A534" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B534" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C534" s="1" t="s">
         <v>1309</v>
       </c>
-      <c r="B534" t="s">
-        <v>1310</v>
-      </c>
-      <c r="C534" s="1" t="s">
-        <v>1311</v>
-      </c>
       <c r="D534" t="s">
         <v>8</v>
       </c>
       <c r="E534" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="535" spans="1:5">
       <c r="A535" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="B535" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="C535" s="1" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="D535" t="s">
         <v>8</v>
@@ -13433,30 +13460,30 @@
     </row>
     <row r="536" spans="1:5">
       <c r="A536" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="B536" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="C536" s="1" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D536" t="s">
         <v>8</v>
       </c>
       <c r="E536" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="537" spans="1:5">
       <c r="A537" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B537" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C537" s="1" t="s">
         <v>1316</v>
-      </c>
-      <c r="B537" t="s">
-        <v>1310</v>
-      </c>
-      <c r="C537" s="1" t="s">
-        <v>1317</v>
       </c>
       <c r="D537" t="s">
         <v>8</v>
@@ -13467,16 +13494,16 @@
     </row>
     <row r="538" spans="1:5">
       <c r="A538" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B538" t="s">
         <v>1318</v>
-      </c>
-      <c r="B538" t="s">
-        <v>1310</v>
       </c>
       <c r="C538" s="1" t="s">
         <v>1319</v>
       </c>
       <c r="D538" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="E538" t="b">
         <v>0</v>
@@ -13487,44 +13514,44 @@
         <v>1320</v>
       </c>
       <c r="B539" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C539" s="1" t="s">
         <v>1321</v>
       </c>
-      <c r="C539" s="1" t="s">
-        <v>1322</v>
-      </c>
       <c r="D539" t="s">
         <v>8</v>
       </c>
       <c r="E539" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="540" spans="1:5">
       <c r="A540" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B540" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C540" s="1" t="s">
         <v>1323</v>
       </c>
-      <c r="B540" t="s">
-        <v>1321</v>
-      </c>
-      <c r="C540" s="1" t="s">
-        <v>1324</v>
-      </c>
       <c r="D540" t="s">
         <v>8</v>
       </c>
       <c r="E540" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="541" spans="1:5">
       <c r="A541" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B541" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C541" s="1" t="s">
         <v>1325</v>
-      </c>
-      <c r="B541" t="s">
-        <v>1321</v>
-      </c>
-      <c r="C541" s="1" t="s">
-        <v>1326</v>
       </c>
       <c r="D541" t="s">
         <v>8</v>
@@ -13535,33 +13562,36 @@
     </row>
     <row r="542" spans="1:5">
       <c r="A542" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B542" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C542" s="1" t="s">
         <v>1327</v>
       </c>
-      <c r="B542" t="s">
-        <v>1328</v>
-      </c>
-      <c r="C542" s="1" t="s">
-        <v>1329</v>
-      </c>
       <c r="D542" t="s">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E542" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="543" spans="1:5">
       <c r="A543" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B543" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C543" s="1" t="s">
         <v>1330</v>
       </c>
-      <c r="B543" t="s">
-        <v>1328</v>
-      </c>
       <c r="D543" t="s">
         <v>8</v>
       </c>
       <c r="E543" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="544" spans="1:5">
@@ -13569,7 +13599,7 @@
         <v>1331</v>
       </c>
       <c r="B544" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="C544" s="1" t="s">
         <v>1332</v>
@@ -13586,15 +13616,80 @@
         <v>1333</v>
       </c>
       <c r="B545" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C545" s="1" t="s">
         <v>1334</v>
       </c>
-      <c r="C545" s="1" t="s">
+      <c r="D545" t="s">
+        <v>8</v>
+      </c>
+      <c r="E545" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546" spans="1:5">
+      <c r="A546" t="s">
         <v>1335</v>
       </c>
-      <c r="D545" t="s">
-        <v>8</v>
-      </c>
-      <c r="E545" t="b">
+      <c r="B546" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C546" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D546" t="s">
+        <v>8</v>
+      </c>
+      <c r="E546" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="547" spans="1:5">
+      <c r="A547" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B547" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D547" t="s">
+        <v>8</v>
+      </c>
+      <c r="E547" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:5">
+      <c r="A548" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B548" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C548" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="D548" t="s">
+        <v>8</v>
+      </c>
+      <c r="E548" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549" spans="1:5">
+      <c r="A549" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B549" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C549" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D549" t="s">
+        <v>8</v>
+      </c>
+      <c r="E549" t="b">
         <v>1</v>
       </c>
     </row>
@@ -14050,8 +14145,8 @@
     <hyperlink ref="C452" r:id="rId448"/>
     <hyperlink ref="C453" r:id="rId449"/>
     <hyperlink ref="C454" r:id="rId450"/>
-    <hyperlink ref="C456" r:id="rId451"/>
-    <hyperlink ref="C457" r:id="rId452"/>
+    <hyperlink ref="C455" r:id="rId451"/>
+    <hyperlink ref="C456" r:id="rId452"/>
     <hyperlink ref="C458" r:id="rId453"/>
     <hyperlink ref="C459" r:id="rId454"/>
     <hyperlink ref="C460" r:id="rId455"/>
@@ -14069,9 +14164,9 @@
     <hyperlink ref="C472" r:id="rId467"/>
     <hyperlink ref="C473" r:id="rId468"/>
     <hyperlink ref="C474" r:id="rId469"/>
-    <hyperlink ref="C475" r:id="rId470" location="/recherche-pm"/>
+    <hyperlink ref="C475" r:id="rId470"/>
     <hyperlink ref="C476" r:id="rId471"/>
-    <hyperlink ref="C477" r:id="rId472"/>
+    <hyperlink ref="C477" r:id="rId472" location="/recherche-pm"/>
     <hyperlink ref="C478" r:id="rId473"/>
     <hyperlink ref="C479" r:id="rId474"/>
     <hyperlink ref="C480" r:id="rId475"/>
@@ -14107,10 +14202,10 @@
     <hyperlink ref="C510" r:id="rId505"/>
     <hyperlink ref="C511" r:id="rId506"/>
     <hyperlink ref="C512" r:id="rId507"/>
-    <hyperlink ref="C514" r:id="rId508"/>
-    <hyperlink ref="C515" r:id="rId509"/>
-    <hyperlink ref="C516" r:id="rId510"/>
-    <hyperlink ref="C517" r:id="rId511"/>
+    <hyperlink ref="C513" r:id="rId508"/>
+    <hyperlink ref="C514" r:id="rId509"/>
+    <hyperlink ref="C515" r:id="rId510"/>
+    <hyperlink ref="C516" r:id="rId511"/>
     <hyperlink ref="C518" r:id="rId512"/>
     <hyperlink ref="C519" r:id="rId513"/>
     <hyperlink ref="C520" r:id="rId514"/>
@@ -14136,8 +14231,12 @@
     <hyperlink ref="C540" r:id="rId534"/>
     <hyperlink ref="C541" r:id="rId535"/>
     <hyperlink ref="C542" r:id="rId536"/>
-    <hyperlink ref="C544" r:id="rId537"/>
-    <hyperlink ref="C545" r:id="rId538"/>
+    <hyperlink ref="C543" r:id="rId537"/>
+    <hyperlink ref="C544" r:id="rId538"/>
+    <hyperlink ref="C545" r:id="rId539"/>
+    <hyperlink ref="C546" r:id="rId540"/>
+    <hyperlink ref="C548" r:id="rId541"/>
+    <hyperlink ref="C549" r:id="rId542"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
